--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="567">
   <si>
     <t>ID</t>
   </si>
@@ -5805,8 +5805,13 @@
       <c r="D192" s="4">
         <v>1969</v>
       </c>
-      <c r="E192" s="5"/>
-      <c r="F192" s="3"/>
+      <c r="E192" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F192" s="9" t="str">
+        <f>B192&amp;".jpg"</f>
+        <v>陳其德.jpg</v>
+      </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="3">
@@ -8637,7 +8642,9 @@
       <c r="D344" s="4">
         <v>1966</v>
       </c>
-      <c r="E344" s="5"/>
+      <c r="E344" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F344" s="3"/>
     </row>
     <row r="345" spans="1:6">
@@ -11286,7 +11293,9 @@
       <c r="D494" s="4">
         <v>1976</v>
       </c>
-      <c r="E494" s="5"/>
+      <c r="E494" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F494" s="3"/>
     </row>
     <row r="495" spans="1:6">
@@ -11302,7 +11311,9 @@
       <c r="D495" s="4">
         <v>1962</v>
       </c>
-      <c r="E495" s="5"/>
+      <c r="E495" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F495" s="3"/>
     </row>
     <row r="496" spans="1:6">
@@ -11318,7 +11329,9 @@
       <c r="D496" s="4">
         <v>1960</v>
       </c>
-      <c r="E496" s="5"/>
+      <c r="E496" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F496" s="3"/>
     </row>
     <row r="497" spans="1:6">

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents and Settings\youth259\Dropbox\My Briefcase\WIP\網頁程式試作\KM-Election\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents and Settings\youth259\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5027A-841A-43E2-8A57-DDC54A7ABD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="RImly0UfTDRFFPz4o9vlPIUTPNhefenMfCj3RyzmYc0="/>
     </ext>
@@ -1730,7 +1742,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="12"/>
@@ -1802,8 +1814,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1829,9 +1841,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2047,7 +2056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F547"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2276,7 +2285,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
@@ -2288,8 +2297,8 @@
         <v>8</v>
       </c>
       <c r="F12" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>石兆緡.jpg</v>
+        <f>B12&amp;".jpg"</f>
+        <v>石兆瑉.jpg</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2297,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>7</v>
@@ -2310,7 +2319,7 @@
       </c>
       <c r="F13" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>石兆瑉.jpg</v>
+        <v>石兆緡.jpg</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5808,7 +5817,7 @@
       <c r="E192" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F192" s="9" t="str">
+      <c r="F192" s="3" t="str">
         <f>B192&amp;".jpg"</f>
         <v>陳其德.jpg</v>
       </c>
@@ -7509,7 +7518,7 @@
       <c r="E281" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F281" s="9" t="str">
+      <c r="F281" s="3" t="str">
         <f t="shared" si="39"/>
         <v>蔡是民.jpg</v>
       </c>
@@ -10771,7 +10780,7 @@
       <c r="D465" s="4">
         <v>1959</v>
       </c>
-      <c r="E465" s="9" t="s">
+      <c r="E465" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F465" s="3"/>
@@ -10789,7 +10798,7 @@
       <c r="D466" s="4">
         <v>1956</v>
       </c>
-      <c r="E466" s="9" t="s">
+      <c r="E466" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F466" s="3"/>
@@ -10807,7 +10816,7 @@
       <c r="D467" s="4">
         <v>1978</v>
       </c>
-      <c r="E467" s="9" t="s">
+      <c r="E467" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F467" s="3"/>
@@ -10825,7 +10834,7 @@
       <c r="D468" s="4">
         <v>1966</v>
       </c>
-      <c r="E468" s="9" t="s">
+      <c r="E468" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F468" s="3"/>
@@ -10843,7 +10852,7 @@
       <c r="D469" s="4">
         <v>1965</v>
       </c>
-      <c r="E469" s="9" t="s">
+      <c r="E469" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F469" s="3"/>
@@ -10861,7 +10870,7 @@
       <c r="D470" s="4">
         <v>1970</v>
       </c>
-      <c r="E470" s="9" t="s">
+      <c r="E470" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F470" s="3"/>
@@ -10879,7 +10888,7 @@
       <c r="D471" s="4">
         <v>1966</v>
       </c>
-      <c r="E471" s="9" t="s">
+      <c r="E471" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F471" s="3"/>
@@ -10897,7 +10906,7 @@
       <c r="D472" s="4">
         <v>1960</v>
       </c>
-      <c r="E472" s="9" t="s">
+      <c r="E472" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F472" s="3"/>
@@ -10915,7 +10924,7 @@
       <c r="D473" s="4">
         <v>1945</v>
       </c>
-      <c r="E473" s="9" t="s">
+      <c r="E473" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F473" s="3"/>
@@ -10933,7 +10942,7 @@
       <c r="D474" s="4">
         <v>1962</v>
       </c>
-      <c r="E474" s="9" t="s">
+      <c r="E474" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F474" s="3"/>
@@ -11005,7 +11014,7 @@
       <c r="D478" s="4">
         <v>1936</v>
       </c>
-      <c r="E478" s="9" t="s">
+      <c r="E478" s="3" t="s">
         <v>497</v>
       </c>
       <c r="F478" s="3"/>

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents and Settings\youth259\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei40\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5027A-841A-43E2-8A57-DDC54A7ABD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C6CFD4-7219-4D9B-B930-2DCE9FA93AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2158,7 +2158,10 @@
       <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="str">
+        <f>B5&amp;".jpg"</f>
+        <v>王石堆.jpg</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3">
@@ -3138,7 +3141,7 @@
         <v>8</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f t="shared" ref="F55:F57" si="10">B55&amp;".jpg"</f>
+        <f t="shared" ref="F55:F59" si="10">B55&amp;".jpg"</f>
         <v>汪成華.jpg</v>
       </c>
     </row>
@@ -3218,7 +3221,10 @@
       <c r="E59" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>辛愛華.jpg</v>
+      </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
@@ -5582,7 +5588,7 @@
         <v>8</v>
       </c>
       <c r="F180" s="3" t="str">
-        <f t="shared" ref="F180:F181" si="28">B180&amp;".jpg"</f>
+        <f t="shared" ref="F180:F182" si="28">B180&amp;".jpg"</f>
         <v>陳玉珍.jpg</v>
       </c>
     </row>
@@ -5623,7 +5629,10 @@
       <c r="E182" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F182" s="3"/>
+      <c r="F182" s="3" t="str">
+        <f t="shared" si="28"/>
+        <v>陳向鑫.jpg</v>
+      </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="3">
@@ -5719,7 +5728,7 @@
         <v>8</v>
       </c>
       <c r="F187" s="3" t="str">
-        <f t="shared" ref="F187:F188" si="30">B187&amp;".jpg"</f>
+        <f t="shared" ref="F187:F190" si="30">B187&amp;".jpg"</f>
         <v>陳志斌.jpg</v>
       </c>
     </row>
@@ -5778,7 +5787,10 @@
       <c r="E190" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F190" s="3"/>
+      <c r="F190" s="3" t="str">
+        <f t="shared" si="30"/>
+        <v>陳秀金.jpg</v>
+      </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="3">
@@ -5855,7 +5867,7 @@
         <v>8</v>
       </c>
       <c r="F194" s="3" t="str">
-        <f t="shared" ref="F194:F195" si="31">B194&amp;".jpg"</f>
+        <f t="shared" ref="F194:F196" si="31">B194&amp;".jpg"</f>
         <v>陳怡利.jpg</v>
       </c>
     </row>
@@ -5894,7 +5906,10 @@
         <v>1949</v>
       </c>
       <c r="E196" s="5"/>
-      <c r="F196" s="3"/>
+      <c r="F196" s="3" t="str">
+        <f t="shared" si="31"/>
+        <v>陳昆第.jpg</v>
+      </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="3">
@@ -6275,7 +6290,10 @@
         <v>1954</v>
       </c>
       <c r="E216" s="5"/>
-      <c r="F216" s="3"/>
+      <c r="F216" s="3" t="str">
+        <f t="shared" ref="F216" si="34">B216&amp;".jpg"</f>
+        <v>陳興坵.jpg</v>
+      </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="3">
@@ -6403,7 +6421,7 @@
         <v>101</v>
       </c>
       <c r="F223" s="3" t="str">
-        <f t="shared" ref="F223:F226" si="34">B223&amp;".jpg"</f>
+        <f t="shared" ref="F223:F226" si="35">B223&amp;".jpg"</f>
         <v>程耀德.jpg</v>
       </c>
     </row>
@@ -6424,7 +6442,7 @@
         <v>32</v>
       </c>
       <c r="F224" s="3" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>黃子誠.jpg</v>
       </c>
     </row>
@@ -6445,7 +6463,7 @@
         <v>8</v>
       </c>
       <c r="F225" s="3" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>黃文欣.jpg</v>
       </c>
     </row>
@@ -6466,7 +6484,7 @@
         <v>8</v>
       </c>
       <c r="F226" s="3" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>黃文麟.jpg</v>
       </c>
     </row>
@@ -6701,7 +6719,10 @@
       <c r="E239" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F239" s="3"/>
+      <c r="F239" s="3" t="str">
+        <f>B239&amp;".jpg"</f>
+        <v>楊水信.jpg</v>
+      </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="3">
@@ -6773,7 +6794,7 @@
         <v>101</v>
       </c>
       <c r="F243" s="3" t="str">
-        <f t="shared" ref="F243:F244" si="35">B243&amp;".jpg"</f>
+        <f t="shared" ref="F243:F244" si="36">B243&amp;".jpg"</f>
         <v>楊育菡.jpg</v>
       </c>
     </row>
@@ -6794,7 +6815,7 @@
         <v>8</v>
       </c>
       <c r="F244" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>楊忠俊.jpg</v>
       </c>
     </row>
@@ -6903,7 +6924,7 @@
         <v>8</v>
       </c>
       <c r="F250" s="3" t="str">
-        <f t="shared" ref="F250:F255" si="36">B250&amp;".jpg"</f>
+        <f t="shared" ref="F250:F255" si="37">B250&amp;".jpg"</f>
         <v>楊肅元.jpg</v>
       </c>
     </row>
@@ -6924,7 +6945,7 @@
         <v>8</v>
       </c>
       <c r="F251" s="3" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>楊萬山.jpg</v>
       </c>
     </row>
@@ -6945,7 +6966,7 @@
         <v>8</v>
       </c>
       <c r="F252" s="3" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>楊榮祥.jpg</v>
       </c>
     </row>
@@ -6966,7 +6987,7 @@
         <v>101</v>
       </c>
       <c r="F253" s="3" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>楊霈璿.jpg</v>
       </c>
     </row>
@@ -6987,7 +7008,7 @@
         <v>8</v>
       </c>
       <c r="F254" s="3" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>楊應雄.jpg</v>
       </c>
     </row>
@@ -7008,7 +7029,7 @@
         <v>8</v>
       </c>
       <c r="F255" s="3" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>楊鎮浯.jpg</v>
       </c>
     </row>
@@ -7215,7 +7236,7 @@
         <v>8</v>
       </c>
       <c r="F266" s="3" t="str">
-        <f t="shared" ref="F266:F270" si="37">B266&amp;".jpg"</f>
+        <f t="shared" ref="F266:F270" si="38">B266&amp;".jpg"</f>
         <v>歐陽彥木.jpg</v>
       </c>
     </row>
@@ -7236,7 +7257,7 @@
         <v>8</v>
       </c>
       <c r="F267" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>歐陽豪.jpg</v>
       </c>
     </row>
@@ -7257,7 +7278,7 @@
         <v>32</v>
       </c>
       <c r="F268" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>歐陽儀雄.jpg</v>
       </c>
     </row>
@@ -7278,7 +7299,7 @@
         <v>8</v>
       </c>
       <c r="F269" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>蔡乃靖.jpg</v>
       </c>
     </row>
@@ -7299,7 +7320,7 @@
         <v>101</v>
       </c>
       <c r="F270" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>蔡云豪.jpg</v>
       </c>
     </row>
@@ -7375,7 +7396,7 @@
         <v>8</v>
       </c>
       <c r="F274" s="3" t="str">
-        <f t="shared" ref="F274:F277" si="38">B274&amp;".jpg"</f>
+        <f t="shared" ref="F274:F277" si="39">B274&amp;".jpg"</f>
         <v>蔡西湖.jpg</v>
       </c>
     </row>
@@ -7396,7 +7417,7 @@
         <v>8</v>
       </c>
       <c r="F275" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>蔡其賀.jpg</v>
       </c>
     </row>
@@ -7417,7 +7438,7 @@
         <v>8</v>
       </c>
       <c r="F276" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>蔡其雍.jpg</v>
       </c>
     </row>
@@ -7438,7 +7459,7 @@
         <v>8</v>
       </c>
       <c r="F277" s="3" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>蔡宗儒.jpg</v>
       </c>
     </row>
@@ -7477,7 +7498,7 @@
         <v>8</v>
       </c>
       <c r="F279" s="3" t="str">
-        <f t="shared" ref="F279:F281" si="39">B279&amp;".jpg"</f>
+        <f t="shared" ref="F279:F281" si="40">B279&amp;".jpg"</f>
         <v>蔡建偉2.jpg</v>
       </c>
     </row>
@@ -7498,7 +7519,7 @@
         <v>8</v>
       </c>
       <c r="F280" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>蔡春生.jpg</v>
       </c>
     </row>
@@ -7519,7 +7540,7 @@
         <v>8</v>
       </c>
       <c r="F281" s="3" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>蔡是民.jpg</v>
       </c>
     </row>
@@ -7558,7 +7579,7 @@
         <v>8</v>
       </c>
       <c r="F283" s="3" t="str">
-        <f t="shared" ref="F283:F284" si="40">B283&amp;".jpg"</f>
+        <f t="shared" ref="F283:F284" si="41">B283&amp;".jpg"</f>
         <v>蔡培榮.jpg</v>
       </c>
     </row>
@@ -7579,7 +7600,7 @@
         <v>8</v>
       </c>
       <c r="F284" s="3" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>蔡連進.jpg</v>
       </c>
     </row>
@@ -7739,7 +7760,7 @@
       </c>
       <c r="E293" s="5"/>
       <c r="F293" s="3" t="str">
-        <f t="shared" ref="F293:F294" si="41">B293&amp;".jpg"</f>
+        <f t="shared" ref="F293:F294" si="42">B293&amp;".jpg"</f>
         <v>鄭志軍.jpg</v>
       </c>
     </row>
@@ -7760,7 +7781,7 @@
         <v>311</v>
       </c>
       <c r="F294" s="3" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>盧月香.jpg</v>
       </c>
     </row>
@@ -8247,7 +8268,10 @@
       <c r="E320" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F320" s="3"/>
+      <c r="F320" s="3" t="str">
+        <f>B320&amp;".jpg"</f>
+        <v>陳水德.jpg</v>
+      </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" s="3">
@@ -8284,7 +8308,7 @@
         <v>8</v>
       </c>
       <c r="F322" s="3" t="str">
-        <f t="shared" ref="F322:F323" si="42">B322&amp;".jpg"</f>
+        <f t="shared" ref="F322:F323" si="43">B322&amp;".jpg"</f>
         <v>周根在.jpg</v>
       </c>
     </row>
@@ -8305,7 +8329,7 @@
         <v>8</v>
       </c>
       <c r="F323" s="3" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>李琳瑯.jpg</v>
       </c>
     </row>
@@ -8344,7 +8368,7 @@
         <v>8</v>
       </c>
       <c r="F325" s="3" t="str">
-        <f t="shared" ref="F325:F326" si="43">B325&amp;".jpg"</f>
+        <f t="shared" ref="F325:F326" si="44">B325&amp;".jpg"</f>
         <v>方水萬.jpg</v>
       </c>
     </row>
@@ -8365,7 +8389,7 @@
         <v>8</v>
       </c>
       <c r="F326" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>蔡金照.jpg</v>
       </c>
     </row>
@@ -8569,7 +8593,10 @@
       <c r="E339" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F339" s="3"/>
+      <c r="F339" s="3" t="str">
+        <f>B339&amp;".jpg"</f>
+        <v>李玉葉.jpg</v>
+      </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" s="3">
@@ -8722,7 +8749,10 @@
         <v>1941</v>
       </c>
       <c r="E348" s="5"/>
-      <c r="F348" s="3"/>
+      <c r="F348" s="3" t="str">
+        <f>B348&amp;".jpg"</f>
+        <v>謝鴻儒.jpg</v>
+      </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" s="3">
@@ -8756,7 +8786,10 @@
         <v>1962</v>
       </c>
       <c r="E350" s="5"/>
-      <c r="F350" s="3"/>
+      <c r="F350" s="3" t="str">
+        <f>B350&amp;".jpg"</f>
+        <v>呂瑞泰.jpg</v>
+      </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" s="3">
@@ -8793,7 +8826,10 @@
         <v>1975</v>
       </c>
       <c r="E352" s="5"/>
-      <c r="F352" s="3"/>
+      <c r="F352" s="3" t="str">
+        <f>B352&amp;".jpg"</f>
+        <v>林金月.jpg</v>
+      </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" s="3">
@@ -9005,7 +9041,10 @@
         <v>1961</v>
       </c>
       <c r="E365" s="5"/>
-      <c r="F365" s="3"/>
+      <c r="F365" s="3" t="str">
+        <f>B365&amp;".jpg"</f>
+        <v>蔡其明.jpg</v>
+      </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="3">
@@ -9069,7 +9108,10 @@
         <v>1981</v>
       </c>
       <c r="E369" s="5"/>
-      <c r="F369" s="3"/>
+      <c r="F369" s="3" t="str">
+        <f>B369&amp;".jpg"</f>
+        <v>蔡怡萱.jpg</v>
+      </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" s="3">

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei40\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C6CFD4-7219-4D9B-B930-2DCE9FA93AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019E712E-FBFB-4899-8A56-2E45A24C00E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4301,7 +4301,10 @@
       <c r="E114" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F114" s="3"/>
+      <c r="F114" s="3" t="str">
+        <f>B114&amp;".jpg"</f>
+        <v>翁文雅.jpg</v>
+      </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="3">
@@ -5769,7 +5772,10 @@
       <c r="E189" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F189" s="3"/>
+      <c r="F189" s="3" t="str">
+        <f t="shared" si="30"/>
+        <v>陳秀治.jpg</v>
+      </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="3">
@@ -8025,7 +8031,10 @@
       <c r="E307" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F307" s="3"/>
+      <c r="F307" s="3" t="str">
+        <f>B307&amp;".jpg"</f>
+        <v>洪嘉莉.jpg</v>
+      </c>
     </row>
     <row r="308" spans="1:6">
       <c r="A308" s="3">
@@ -8770,7 +8779,10 @@
       <c r="E349" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F349" s="3"/>
+      <c r="F349" s="3" t="str">
+        <f>B349&amp;".jpg"</f>
+        <v>關志武.jpg</v>
+      </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="3">
@@ -8913,7 +8925,10 @@
       <c r="E357" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F357" s="3"/>
+      <c r="F357" s="3" t="str">
+        <f>B357&amp;".jpg"</f>
+        <v>許績才.jpg</v>
+      </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" s="3">
@@ -9228,7 +9243,10 @@
         <v>1956</v>
       </c>
       <c r="E376" s="5"/>
-      <c r="F376" s="3"/>
+      <c r="F376" s="3" t="str">
+        <f>B376&amp;".jpg"</f>
+        <v>蔡祥坤.jpg</v>
+      </c>
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="3">
@@ -9281,7 +9299,10 @@
       <c r="E379" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F379" s="3"/>
+      <c r="F379" s="3" t="str">
+        <f>B379&amp;".jpg"</f>
+        <v>楊雨川.jpg</v>
+      </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="3">
@@ -9352,7 +9373,10 @@
       <c r="E383" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F383" s="3"/>
+      <c r="F383" s="3" t="str">
+        <f>B383&amp;".jpg"</f>
+        <v>辛文進.jpg</v>
+      </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="3">
@@ -9386,7 +9410,10 @@
       <c r="E385" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F385" s="3"/>
+      <c r="F385" s="3" t="str">
+        <f>B385&amp;".jpg"</f>
+        <v>黃延良.jpg</v>
+      </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="3">
@@ -9420,7 +9447,10 @@
       <c r="E387" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F387" s="3"/>
+      <c r="F387" s="3" t="str">
+        <f>B387&amp;".jpg"</f>
+        <v>戴德強.jpg</v>
+      </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="3">
@@ -9475,7 +9505,10 @@
       <c r="E390" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F390" s="3"/>
+      <c r="F390" s="3" t="str">
+        <f>B390&amp;".jpg"</f>
+        <v>張瀚龍.jpg</v>
+      </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="3">
@@ -9511,7 +9544,10 @@
       <c r="E392" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F392" s="3"/>
+      <c r="F392" s="3" t="str">
+        <f>B392&amp;".jpg"</f>
+        <v>陳賜發.jpg</v>
+      </c>
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="3">
@@ -9619,7 +9655,10 @@
       <c r="E398" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="F398" s="3"/>
+      <c r="F398" s="3" t="str">
+        <f>B398&amp;".jpg"</f>
+        <v>陳文傑.jpg</v>
+      </c>
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="3">
@@ -9637,7 +9676,10 @@
       <c r="E399" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F399" s="3"/>
+      <c r="F399" s="3" t="str">
+        <f>B399&amp;".jpg"</f>
+        <v>陳福林.jpg</v>
+      </c>
     </row>
     <row r="400" spans="1:6">
       <c r="A400" s="3">
@@ -9673,7 +9715,10 @@
       <c r="E401" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F401" s="3"/>
+      <c r="F401" s="3" t="str">
+        <f>B401&amp;".jpg"</f>
+        <v>黃添丁.jpg</v>
+      </c>
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="3">
@@ -9727,7 +9772,10 @@
       <c r="E404" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F404" s="3"/>
+      <c r="F404" s="3" t="str">
+        <f>B404&amp;".jpg"</f>
+        <v>楊恭勤.jpg</v>
+      </c>
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="3">
@@ -9745,7 +9793,10 @@
       <c r="E405" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F405" s="3"/>
+      <c r="F405" s="3" t="str">
+        <f>B405&amp;".jpg"</f>
+        <v>周家才.jpg</v>
+      </c>
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="3">
@@ -9799,7 +9850,10 @@
       <c r="E408" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F408" s="3"/>
+      <c r="F408" s="3" t="str">
+        <f>B408&amp;".jpg"</f>
+        <v>吳孟霖.jpg</v>
+      </c>
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="3">
@@ -9817,7 +9871,10 @@
       <c r="E409" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F409" s="3"/>
+      <c r="F409" s="3" t="str">
+        <f>B409&amp;".jpg"</f>
+        <v>陳晚開.jpg</v>
+      </c>
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="3">
@@ -9853,7 +9910,10 @@
       <c r="E411" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F411" s="3"/>
+      <c r="F411" s="3" t="str">
+        <f>B411&amp;".jpg"</f>
+        <v>陳偃武.jpg</v>
+      </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="3">
@@ -9871,7 +9931,10 @@
       <c r="E412" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F412" s="3"/>
+      <c r="F412" s="3" t="str">
+        <f>B412&amp;".jpg"</f>
+        <v>謝慶閣.jpg</v>
+      </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="3">
@@ -9907,7 +9970,10 @@
       <c r="E414" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F414" s="3"/>
+      <c r="F414" s="3" t="str">
+        <f>B414&amp;".jpg"</f>
+        <v>蔡懷芝.jpg</v>
+      </c>
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="3">
@@ -9925,7 +9991,10 @@
       <c r="E415" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F415" s="3"/>
+      <c r="F415" s="3" t="str">
+        <f>B415&amp;".jpg"</f>
+        <v>陳錦章.jpg</v>
+      </c>
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="3">
@@ -9961,7 +10030,10 @@
       <c r="E417" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F417" s="3"/>
+      <c r="F417" s="3" t="str">
+        <f>B417&amp;".jpg"</f>
+        <v>黃建忠.jpg</v>
+      </c>
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="3">
@@ -9979,7 +10051,10 @@
       <c r="E418" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F418" s="3"/>
+      <c r="F418" s="3" t="str">
+        <f>B418&amp;".jpg"</f>
+        <v>呂永林.jpg</v>
+      </c>
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="3">
@@ -10015,7 +10090,10 @@
       <c r="E420" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F420" s="3"/>
+      <c r="F420" s="3" t="str">
+        <f>B420&amp;".jpg"</f>
+        <v>許三進.jpg</v>
+      </c>
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="3">
@@ -10033,7 +10111,10 @@
       <c r="E421" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F421" s="3"/>
+      <c r="F421" s="3" t="str">
+        <f>B421&amp;".jpg"</f>
+        <v>許明吉.jpg</v>
+      </c>
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="3">
@@ -10051,7 +10132,10 @@
       <c r="E422" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F422" s="3"/>
+      <c r="F422" s="3" t="str">
+        <f>B422&amp;".jpg"</f>
+        <v>楊振嵩.jpg</v>
+      </c>
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="3">
@@ -10069,7 +10153,10 @@
       <c r="E423" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F423" s="3"/>
+      <c r="F423" s="3" t="str">
+        <f>B423&amp;".jpg"</f>
+        <v>楊龍傳.jpg</v>
+      </c>
     </row>
     <row r="424" spans="1:6">
       <c r="A424" s="3">
@@ -10087,7 +10174,10 @@
       <c r="E424" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F424" s="3"/>
+      <c r="F424" s="3" t="str">
+        <f>B424&amp;".jpg"</f>
+        <v>翁明海.jpg</v>
+      </c>
     </row>
     <row r="425" spans="1:6">
       <c r="A425" s="3">
@@ -10105,7 +10195,10 @@
       <c r="E425" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F425" s="3"/>
+      <c r="F425" s="3" t="str">
+        <f>B425&amp;".jpg"</f>
+        <v>翁品洋.jpg</v>
+      </c>
     </row>
     <row r="426" spans="1:6">
       <c r="A426" s="3">
@@ -10123,7 +10216,10 @@
       <c r="E426" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F426" s="3"/>
+      <c r="F426" s="3" t="str">
+        <f>B426&amp;".jpg"</f>
+        <v>洪天南.jpg</v>
+      </c>
     </row>
     <row r="427" spans="1:6">
       <c r="A427" s="3">
@@ -10159,7 +10255,10 @@
       <c r="E428" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F428" s="3"/>
+      <c r="F428" s="3" t="str">
+        <f>B428&amp;".jpg"</f>
+        <v>蔡福榮.jpg</v>
+      </c>
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="3">
@@ -10195,7 +10294,10 @@
       <c r="E430" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F430" s="3"/>
+      <c r="F430" s="3" t="str">
+        <f>B430&amp;".jpg"</f>
+        <v>林龍照.jpg</v>
+      </c>
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="3">
@@ -10285,7 +10387,10 @@
       <c r="E435" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F435" s="3"/>
+      <c r="F435" s="3" t="str">
+        <f>B435&amp;".jpg"</f>
+        <v>莊金蓮.jpg</v>
+      </c>
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="3">
@@ -10663,7 +10768,10 @@
       <c r="E456" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F456" s="3"/>
+      <c r="F456" s="3" t="str">
+        <f>B456&amp;".jpg"</f>
+        <v>吳志成.jpg</v>
+      </c>
     </row>
     <row r="457" spans="1:6">
       <c r="A457" s="3">
@@ -10699,7 +10807,10 @@
       <c r="E458" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F458" s="3"/>
+      <c r="F458" s="3" t="str">
+        <f>B458&amp;".jpg"</f>
+        <v>蔡顯明.jpg</v>
+      </c>
     </row>
     <row r="459" spans="1:6">
       <c r="A459" s="3">
@@ -11167,7 +11278,10 @@
       <c r="E484" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F484" s="3"/>
+      <c r="F484" s="3" t="str">
+        <f>B484&amp;".jpg"</f>
+        <v>李朝金.jpg</v>
+      </c>
     </row>
     <row r="485" spans="1:6">
       <c r="A485" s="3">
@@ -11203,7 +11317,10 @@
       <c r="E486" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F486" s="3"/>
+      <c r="F486" s="3" t="str">
+        <f>B486&amp;".jpg"</f>
+        <v>蔡輝進.jpg</v>
+      </c>
     </row>
     <row r="487" spans="1:6">
       <c r="A487" s="3">
@@ -12188,7 +12305,10 @@
         <v>1956</v>
       </c>
       <c r="E546" s="5"/>
-      <c r="F546" s="3"/>
+      <c r="F546" s="3" t="str">
+        <f>B546&amp;".jpg"</f>
+        <v>吳有祥.jpg</v>
+      </c>
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="3">

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei40\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019E712E-FBFB-4899-8A56-2E45A24C00E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BEF031-2BA4-4C8F-9B2C-67FCA02E477E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6930,7 +6930,7 @@
         <v>8</v>
       </c>
       <c r="F250" s="3" t="str">
-        <f t="shared" ref="F250:F255" si="37">B250&amp;".jpg"</f>
+        <f t="shared" ref="F250:F256" si="37">B250&amp;".jpg"</f>
         <v>楊肅元.jpg</v>
       </c>
     </row>
@@ -7055,7 +7055,10 @@
       <c r="E256" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F256" s="3"/>
+      <c r="F256" s="3" t="str">
+        <f t="shared" si="37"/>
+        <v>楊耀芸.jpg</v>
+      </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="3">
@@ -9754,7 +9757,10 @@
       <c r="E403" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F403" s="3"/>
+      <c r="F403" s="3" t="str">
+        <f>B403&amp;".jpg"</f>
+        <v>黃志明.jpg</v>
+      </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="3">
@@ -10091,7 +10097,7 @@
         <v>8</v>
       </c>
       <c r="F420" s="3" t="str">
-        <f>B420&amp;".jpg"</f>
+        <f t="shared" ref="F420:F426" si="45">B420&amp;".jpg"</f>
         <v>許三進.jpg</v>
       </c>
     </row>
@@ -10112,7 +10118,7 @@
         <v>8</v>
       </c>
       <c r="F421" s="3" t="str">
-        <f>B421&amp;".jpg"</f>
+        <f t="shared" si="45"/>
         <v>許明吉.jpg</v>
       </c>
     </row>
@@ -10133,7 +10139,7 @@
         <v>8</v>
       </c>
       <c r="F422" s="3" t="str">
-        <f>B422&amp;".jpg"</f>
+        <f t="shared" si="45"/>
         <v>楊振嵩.jpg</v>
       </c>
     </row>
@@ -10154,7 +10160,7 @@
         <v>8</v>
       </c>
       <c r="F423" s="3" t="str">
-        <f>B423&amp;".jpg"</f>
+        <f t="shared" si="45"/>
         <v>楊龍傳.jpg</v>
       </c>
     </row>
@@ -10175,7 +10181,7 @@
         <v>8</v>
       </c>
       <c r="F424" s="3" t="str">
-        <f>B424&amp;".jpg"</f>
+        <f t="shared" si="45"/>
         <v>翁明海.jpg</v>
       </c>
     </row>
@@ -10196,7 +10202,7 @@
         <v>8</v>
       </c>
       <c r="F425" s="3" t="str">
-        <f>B425&amp;".jpg"</f>
+        <f t="shared" si="45"/>
         <v>翁品洋.jpg</v>
       </c>
     </row>
@@ -10217,7 +10223,7 @@
         <v>8</v>
       </c>
       <c r="F426" s="3" t="str">
-        <f>B426&amp;".jpg"</f>
+        <f t="shared" si="45"/>
         <v>洪天南.jpg</v>
       </c>
     </row>
@@ -10624,7 +10630,10 @@
       <c r="E448" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F448" s="3"/>
+      <c r="F448" s="3" t="str">
+        <f>B448&amp;".jpg"</f>
+        <v>盧志嶢.jpg</v>
+      </c>
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="3">
@@ -10900,7 +10909,10 @@
       <c r="E463" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F463" s="3"/>
+      <c r="F463" s="3" t="str">
+        <f>B463&amp;".jpg"</f>
+        <v>呂光河.jpg</v>
+      </c>
     </row>
     <row r="464" spans="1:6">
       <c r="A464" s="3">
@@ -10936,7 +10948,10 @@
       <c r="E465" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F465" s="3"/>
+      <c r="F465" s="3" t="str">
+        <f>B465&amp;".jpg"</f>
+        <v>李賢慨.jpg</v>
+      </c>
     </row>
     <row r="466" spans="1:6">
       <c r="A466" s="3">
@@ -11152,7 +11167,10 @@
       <c r="E477" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F477" s="3"/>
+      <c r="F477" s="3" t="str">
+        <f>B477&amp;".jpg"</f>
+        <v>方耀年.jpg</v>
+      </c>
     </row>
     <row r="478" spans="1:6">
       <c r="A478" s="3">
@@ -11242,7 +11260,10 @@
       <c r="E482" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F482" s="3"/>
+      <c r="F482" s="3" t="str">
+        <f>B482&amp;".jpg"</f>
+        <v>黃國民.jpg</v>
+      </c>
     </row>
     <row r="483" spans="1:6">
       <c r="A483" s="3">
@@ -11260,7 +11281,10 @@
       <c r="E483" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F483" s="3"/>
+      <c r="F483" s="3" t="str">
+        <f>B483&amp;".jpg"</f>
+        <v>歐贊隊.jpg</v>
+      </c>
     </row>
     <row r="484" spans="1:6">
       <c r="A484" s="3">
@@ -11338,7 +11362,10 @@
       <c r="E487" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F487" s="3"/>
+      <c r="F487" s="3" t="str">
+        <f>B487&amp;".jpg"</f>
+        <v>楊朝基.jpg</v>
+      </c>
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="3">
@@ -11446,7 +11473,10 @@
       <c r="E493" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F493" s="3"/>
+      <c r="F493" s="3" t="str">
+        <f>B493&amp;".jpg"</f>
+        <v>呂玉華.jpg</v>
+      </c>
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="3">
@@ -11516,7 +11546,10 @@
         <v>1976</v>
       </c>
       <c r="E497" s="5"/>
-      <c r="F497" s="3"/>
+      <c r="F497" s="3" t="str">
+        <f>B497&amp;".jpg"</f>
+        <v>林照人.jpg</v>
+      </c>
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="3">
@@ -11532,7 +11565,10 @@
         <v>1957</v>
       </c>
       <c r="E498" s="5"/>
-      <c r="F498" s="3"/>
+      <c r="F498" s="3" t="str">
+        <f>B498&amp;".jpg"</f>
+        <v>林開興.jpg</v>
+      </c>
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="3">

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei40\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BEF031-2BA4-4C8F-9B2C-67FCA02E477E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6378D854-B089-41D1-9DEF-659710427819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12313,7 +12313,7 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" s="3">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B545" s="4" t="s">
         <v>564</v>
@@ -12329,7 +12329,7 @@
     </row>
     <row r="546" spans="1:6">
       <c r="A546" s="3">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B546" s="4" t="s">
         <v>565</v>
@@ -12348,7 +12348,7 @@
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="3">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B547" s="4" t="s">
         <v>566</v>

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei40\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents and Settings\youth259\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6378D854-B089-41D1-9DEF-659710427819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="569">
   <si>
     <t>ID</t>
   </si>
@@ -1737,12 +1736,20 @@
   </si>
   <si>
     <t>莊素雲</t>
+  </si>
+  <si>
+    <t>福建省莆田縣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>高雄市</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5">
     <font>
       <sz val="12"/>
@@ -2056,7 +2063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F547"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2983,7 +2990,9 @@
       <c r="D47" s="4">
         <v>1954</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F47" s="3"/>
     </row>
     <row r="48" spans="1:6">
@@ -5853,7 +5862,9 @@
       <c r="D193" s="4">
         <v>1970</v>
       </c>
-      <c r="E193" s="5"/>
+      <c r="E193" s="5" t="s">
+        <v>568</v>
+      </c>
       <c r="F193" s="3"/>
     </row>
     <row r="194" spans="1:6">
@@ -5951,7 +5962,9 @@
       <c r="D198" s="4">
         <v>1961</v>
       </c>
-      <c r="E198" s="5"/>
+      <c r="E198" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F198" s="3"/>
     </row>
     <row r="199" spans="1:6">
@@ -6282,7 +6295,7 @@
       </c>
       <c r="F215" s="3"/>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" ht="15.6">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -6295,7 +6308,9 @@
       <c r="D216" s="4">
         <v>1954</v>
       </c>
-      <c r="E216" s="5"/>
+      <c r="E216" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F216" s="3" t="str">
         <f t="shared" ref="F216" si="34">B216&amp;".jpg"</f>
         <v>陳興坵.jpg</v>
@@ -7050,7 +7065,7 @@
         <v>7</v>
       </c>
       <c r="D256" s="4">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E256" s="5" t="s">
         <v>8</v>
@@ -7167,7 +7182,7 @@
         <v>14</v>
       </c>
       <c r="D262" s="4">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>8</v>
@@ -7694,7 +7709,9 @@
       <c r="D289" s="4">
         <v>1961</v>
       </c>
-      <c r="E289" s="5"/>
+      <c r="E289" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F289" s="3"/>
     </row>
     <row r="290" spans="1:6">
@@ -8893,7 +8910,9 @@
       <c r="D355" s="4">
         <v>1960</v>
       </c>
-      <c r="E355" s="5"/>
+      <c r="E355" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F355" s="3"/>
     </row>
     <row r="356" spans="1:6">
@@ -11545,7 +11564,9 @@
       <c r="D497" s="4">
         <v>1976</v>
       </c>
-      <c r="E497" s="5"/>
+      <c r="E497" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F497" s="3" t="str">
         <f>B497&amp;".jpg"</f>
         <v>林照人.jpg</v>
@@ -11564,7 +11585,9 @@
       <c r="D498" s="4">
         <v>1957</v>
       </c>
-      <c r="E498" s="5"/>
+      <c r="E498" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F498" s="3" t="str">
         <f>B498&amp;".jpg"</f>
         <v>林開興.jpg</v>
@@ -11583,7 +11606,9 @@
       <c r="D499" s="4">
         <v>1938</v>
       </c>
-      <c r="E499" s="5"/>
+      <c r="E499" s="5" t="s">
+        <v>567</v>
+      </c>
       <c r="F499" s="3"/>
     </row>
     <row r="500" spans="1:6">
@@ -11599,7 +11624,9 @@
       <c r="D500" s="4">
         <v>1950</v>
       </c>
-      <c r="E500" s="5"/>
+      <c r="E500" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="F500" s="3"/>
     </row>
     <row r="501" spans="1:6">

--- a/candidates.xlsx
+++ b/candidates.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents and Settings\youth259\Dropbox\My Briefcase\WIP\網頁程式試作\km-election\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei40\Dropbox\My Briefcase\Coding\km-election\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D61F5C-B9ED-4C60-A112-08805A6B4E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1749,7 +1750,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="12"/>
@@ -2063,7 +2064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F547"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2072,7 +2073,7 @@
     <col min="6" max="6" width="18.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2092,7 +2093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" ht="15.6">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>方駿洋.jpg</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="15.6">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2131,7 +2132,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="15.6">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2149,7 +2150,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="15.6">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2170,7 +2171,7 @@
         <v>王石堆.jpg</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="15.6">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2188,7 +2189,7 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="15.6">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2209,7 +2210,7 @@
         <v>王秀玉.jpg</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="15.6">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2230,7 +2231,7 @@
         <v>王國代.jpg</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="15.6">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2248,7 +2249,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="15.6">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2269,7 +2270,7 @@
         <v>王碧珍.jpg</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="15.6">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2290,7 +2291,7 @@
         <v>石永城.jpg</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" ht="15.6">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>石兆瑉.jpg</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="15.6">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>石兆緡.jpg</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" ht="15.6">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2350,7 +2351,7 @@
       </c>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="15.6">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>朱紀瑋.jpg</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="15.6">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>何開忠.jpg</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15.6">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2413,7 +2414,7 @@
         <v>吳成典.jpg</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="15.6">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2431,7 +2432,7 @@
       </c>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="15.6">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2452,7 +2453,7 @@
         <v>吳有家.jpg</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" ht="15.6">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2473,7 +2474,7 @@
         <v>吳伯揚.jpg</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="15.6">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2494,7 +2495,7 @@
         <v>吳佩雯.jpg</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="15.6">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2510,7 +2511,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" ht="15.6">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2528,7 +2529,7 @@
       </c>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="15.6">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -2546,7 +2547,7 @@
       </c>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" ht="15.6">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -2567,7 +2568,7 @@
         <v>吳嘉將.jpg</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" ht="15.6">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2588,7 +2589,7 @@
         <v>吳福全.jpg</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" ht="15.6">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -2609,7 +2610,7 @@
         <v>吳增允.jpg</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" ht="15.6">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -2627,7 +2628,7 @@
       </c>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" ht="15.6">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>呂錦同.jpg</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" ht="15.6">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -2669,7 +2670,7 @@
         <v>呂寶玉.jpg</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" ht="15.6">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -2687,7 +2688,7 @@
       </c>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" ht="15.6">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -2703,7 +2704,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" ht="15.6">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -2724,7 +2725,7 @@
         <v>李正騰.jpg</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" ht="15.6">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>李成義.jpg</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" ht="15.6">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -2763,7 +2764,7 @@
       </c>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="15.6">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>李志鴻.jpg</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" ht="15.6">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -2805,7 +2806,7 @@
         <v>李沃士.jpg</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" ht="15.6">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>李秀華.jpg</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" ht="15.6">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -2844,7 +2845,7 @@
       </c>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" ht="15.6">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -2865,7 +2866,7 @@
         <v>李俊龍.jpg</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" ht="15.6">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -2881,7 +2882,7 @@
       <c r="E41" s="5"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" ht="15.6">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" ht="15.6">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -2917,7 +2918,7 @@
       </c>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" ht="15.6">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>李炷烽.jpg</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" ht="15.6">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>李誠智.jpg</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" ht="15.6">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -2977,7 +2978,7 @@
       </c>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" ht="15.6">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -2995,7 +2996,7 @@
       </c>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" ht="15.6">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -3016,7 +3017,7 @@
         <v>李養生.jpg</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" ht="15.6">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -3034,7 +3035,7 @@
       </c>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" ht="15.6">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -3052,7 +3053,7 @@
       </c>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" ht="15.6">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -3073,7 +3074,7 @@
         <v>李錫添.jpg</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" ht="15.6">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -3094,7 +3095,7 @@
         <v>李錫瑜.jpg</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" ht="15.6">
       <c r="A53" s="3">
         <v>51</v>
       </c>
@@ -3115,7 +3116,7 @@
         <v>李應文.jpg</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" ht="15.6">
       <c r="A54" s="3">
         <v>52</v>
       </c>
@@ -3133,7 +3134,7 @@
       </c>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" ht="15.6">
       <c r="A55" s="3">
         <v>53</v>
       </c>
@@ -3154,7 +3155,7 @@
         <v>汪成華.jpg</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" ht="15.6">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>汪承樺.jpg</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" ht="15.6">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -3196,7 +3197,7 @@
         <v>汪松威.jpg</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" ht="15.6">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -3214,7 +3215,7 @@
       </c>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" ht="15.6">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -3235,7 +3236,7 @@
         <v>辛愛華.jpg</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" ht="15.6">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -3256,7 +3257,7 @@
         <v>周子傑.jpg</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" ht="15.6">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -3277,7 +3278,7 @@
         <v>周水土.jpg</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" ht="15.6">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -3295,7 +3296,7 @@
       </c>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" ht="15.6">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -3313,7 +3314,7 @@
       </c>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" ht="15.6">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -3329,7 +3330,7 @@
       <c r="E64" s="5"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" ht="15.6">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -3350,7 +3351,7 @@
         <v>周曉芸.jpg</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" ht="15.6">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -3371,7 +3372,7 @@
         <v>尚文凱.jpg</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" ht="15.6">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -3389,7 +3390,7 @@
       </c>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" ht="15.6">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -3407,7 +3408,7 @@
       </c>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" ht="15.6">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -3428,7 +3429,7 @@
         <v>林志錦.jpg</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" ht="15.6">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -3449,7 +3450,7 @@
         <v>林宜蘭.jpg</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" ht="15.6">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -3470,7 +3471,7 @@
         <v>林金英.jpg</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" ht="15.6">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -3491,7 +3492,7 @@
         <v>林金量.jpg</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" ht="15.6">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -3512,7 +3513,7 @@
         <v>林長征.jpg</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" ht="15.6">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -3533,7 +3534,7 @@
         <v>林長耕.jpg</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" ht="15.6">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -3554,7 +3555,7 @@
         <v>林長鴻.jpg</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" ht="15.6">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -3570,7 +3571,7 @@
       <c r="E76" s="5"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" ht="15.6">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -3588,7 +3589,7 @@
       </c>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" ht="15.6">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>林孫全.jpg</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" ht="15.6">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -3627,7 +3628,7 @@
       </c>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" ht="15.6">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -3643,7 +3644,7 @@
       <c r="E80" s="5"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" ht="15.6">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -3659,7 +3660,7 @@
       <c r="E81" s="5"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" ht="15.6">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -3680,7 +3681,7 @@
         <v>林嘉森.jpg</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" ht="15.6">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -3698,7 +3699,7 @@
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" ht="15.6">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -3716,7 +3717,7 @@
       </c>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" ht="15.6">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -3737,7 +3738,7 @@
         <v>林麗芬.jpg</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" ht="15.6">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -3758,7 +3759,7 @@
         <v>洪允典.jpg</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" ht="15.6">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -3779,7 +3780,7 @@
         <v>洪正.jpg</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" ht="15.6">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -3800,7 +3801,7 @@
         <v>洪成發.jpg</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" ht="15.6">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -3821,7 +3822,7 @@
         <v>洪志恒.jpg</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" ht="15.6">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -3842,7 +3843,7 @@
         <v>洪和成.jpg</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" ht="15.6">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -3863,7 +3864,7 @@
         <v>洪若珊.jpg</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" ht="15.6">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -3881,7 +3882,7 @@
       </c>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" ht="15.6">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -3902,7 +3903,7 @@
         <v>洪海水.jpg</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" ht="15.6">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -3923,7 +3924,7 @@
         <v>洪健中.jpg</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" ht="15.6">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -3939,7 +3940,7 @@
       <c r="E95" s="5"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" ht="15.6">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -3960,7 +3961,7 @@
         <v>洪雅明.jpg</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" ht="15.6">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -3978,7 +3979,7 @@
       </c>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" ht="15.6">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -3994,7 +3995,7 @@
       <c r="E98" s="5"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" ht="15.6">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -4015,7 +4016,7 @@
         <v>洪輝榮.jpg</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" ht="15.6">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -4036,7 +4037,7 @@
         <v>洪燕玉.jpg</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" ht="15.6">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -4054,7 +4055,7 @@
       </c>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" ht="15.6">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -4075,7 +4076,7 @@
         <v>洪鴻斌.jpg</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" ht="15.6">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -4096,7 +4097,7 @@
         <v>洪麗萍.jpg</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" ht="15.6">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -4117,7 +4118,7 @@
         <v>胡偉生.jpg</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" ht="15.6">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>胡凱宇.jpg</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" ht="15.6">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -4159,7 +4160,7 @@
         <v>倪于媃.jpg</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" ht="15.6">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -4177,7 +4178,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" ht="15.6">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>唐惠霈.jpg</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" ht="15.6">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -4219,7 +4220,7 @@
         <v>唐麗輝.jpg</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" ht="15.6">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -4237,7 +4238,7 @@
       </c>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" ht="15.6">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -4258,7 +4259,7 @@
         <v>徐銀磯.jpg</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" ht="15.6">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -4276,7 +4277,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" ht="15.6">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -4294,7 +4295,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" ht="15.6">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -4315,7 +4316,7 @@
         <v>翁文雅.jpg</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" ht="15.6">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -4336,7 +4337,7 @@
         <v>翁文奧.jpg</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" ht="15.6">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -4352,7 +4353,7 @@
       <c r="E116" s="5"/>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" ht="15.6">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -4370,7 +4371,7 @@
       </c>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" ht="15.6">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -4391,7 +4392,7 @@
         <v>翁沂杰.jpg</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" ht="15.6">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -4412,7 +4413,7 @@
         <v>翁明志.jpg</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" ht="15.6">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -4430,7 +4431,7 @@
       </c>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" ht="15.6">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>翁明惠.jpg</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" ht="15.6">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -4469,7 +4470,7 @@
       </c>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" ht="15.6">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -4487,7 +4488,7 @@
       </c>
       <c r="F123" s="3"/>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" ht="15.6">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -4508,7 +4509,7 @@
         <v>翁裕凱.jpg</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" ht="15.6">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -4529,7 +4530,7 @@
         <v>翁銘駿.jpg</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" ht="15.6">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -4550,7 +4551,7 @@
         <v>馬自壯.jpg</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" ht="15.6">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -4571,7 +4572,7 @@
         <v>高丹華.jpg</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" ht="15.6">
       <c r="A128" s="3">
         <v>124</v>
       </c>
@@ -4592,7 +4593,7 @@
         <v>高丹樺.jpg</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" ht="15.6">
       <c r="A129" s="3">
         <v>125</v>
       </c>
@@ -4610,7 +4611,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" ht="15.6">
       <c r="A130" s="3">
         <v>126</v>
       </c>
@@ -4631,7 +4632,7 @@
         <v>高絃騰.jpg</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" ht="15.6">
       <c r="A131" s="3">
         <v>127</v>
       </c>
@@ -4652,7 +4653,7 @@
         <v>張中法.jpg</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" ht="15.6">
       <c r="A132" s="3">
         <v>128</v>
       </c>
@@ -4673,7 +4674,7 @@
         <v>張天欽.jpg</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" ht="15.6">
       <c r="A133" s="3">
         <v>129</v>
       </c>
@@ -4691,7 +4692,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" ht="15.6">
       <c r="A134" s="3">
         <v>130</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>張成爵.jpg</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" ht="15.6">
       <c r="A135" s="3">
         <v>131</v>
       </c>
@@ -4730,7 +4731,7 @@
       </c>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" ht="15.6">
       <c r="A136" s="3">
         <v>132</v>
       </c>
@@ -4748,7 +4749,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" ht="15.6">
       <c r="A137" s="3">
         <v>133</v>
       </c>
@@ -4764,7 +4765,7 @@
       <c r="E137" s="5"/>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" ht="15.6">
       <c r="A138" s="3">
         <v>134</v>
       </c>
@@ -4785,7 +4786,7 @@
         <v>張貴富.jpg</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" ht="15.6">
       <c r="A139" s="3">
         <v>135</v>
       </c>
@@ -4806,7 +4807,7 @@
         <v>張雲量.jpg</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" ht="15.6">
       <c r="A140" s="3">
         <v>136</v>
       </c>
@@ -4827,7 +4828,7 @@
         <v>張雲德.jpg</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" ht="15.6">
       <c r="A141" s="3">
         <v>137</v>
       </c>
@@ -4845,7 +4846,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" ht="15.6">
       <c r="A142" s="3">
         <v>138</v>
       </c>
@@ -4863,7 +4864,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" ht="15.6">
       <c r="A143" s="3">
         <v>139</v>
       </c>
@@ -4881,7 +4882,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" ht="15.6">
       <c r="A144" s="3">
         <v>140</v>
       </c>
@@ -4899,7 +4900,7 @@
       </c>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" ht="15.6">
       <c r="A145" s="3">
         <v>141</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v>莊旭英.jpg</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" ht="15.6">
       <c r="A146" s="3">
         <v>142</v>
       </c>
@@ -4938,7 +4939,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" ht="15.6">
       <c r="A147" s="3">
         <v>143</v>
       </c>
@@ -4956,7 +4957,7 @@
       </c>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" ht="15.6">
       <c r="A148" s="3">
         <v>144</v>
       </c>
@@ -4974,7 +4975,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" ht="15.6">
       <c r="A149" s="3">
         <v>145</v>
       </c>
@@ -4995,7 +4996,7 @@
         <v>莊嘉銘.jpg</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" ht="15.6">
       <c r="A150" s="3">
         <v>146</v>
       </c>
@@ -5016,7 +5017,7 @@
         <v>許乃權.jpg</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" ht="15.6">
       <c r="A151" s="3">
         <v>147</v>
       </c>
@@ -5037,7 +5038,7 @@
         <v>許大鴻.jpg</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" ht="15.6">
       <c r="A152" s="3">
         <v>148</v>
       </c>
@@ -5055,7 +5056,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" ht="15.6">
       <c r="A153" s="3">
         <v>149</v>
       </c>
@@ -5076,7 +5077,7 @@
         <v>許丕肯.jpg</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" ht="15.6">
       <c r="A154" s="3">
         <v>150</v>
       </c>
@@ -5094,7 +5095,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" ht="15.6">
       <c r="A155" s="3">
         <v>151</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>許玉昭.jpg</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" ht="15.6">
       <c r="A156" s="3">
         <v>152</v>
       </c>
@@ -5136,7 +5137,7 @@
         <v>許志猛.jpg</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" ht="15.6">
       <c r="A157" s="3">
         <v>153</v>
       </c>
@@ -5154,7 +5155,7 @@
       </c>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" ht="15.6">
       <c r="A158" s="3">
         <v>154</v>
       </c>
@@ -5172,7 +5173,7 @@
       </c>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" ht="15.6">
       <c r="A159" s="3">
         <v>155</v>
       </c>
@@ -5193,7 +5194,7 @@
         <v>許建中.jpg</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" ht="15.6">
       <c r="A160" s="3">
         <v>156</v>
       </c>
@@ -5214,7 +5215,7 @@
         <v>許華玉.jpg</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" ht="15.6">
       <c r="A161" s="3">
         <v>157</v>
       </c>
@@ -5235,7 +5236,7 @@
         <v>許慧新.jpg</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" ht="15.6">
       <c r="A162" s="3">
         <v>158</v>
       </c>
@@ -5253,7 +5254,7 @@
       </c>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" ht="15.6">
       <c r="A163" s="3">
         <v>159</v>
       </c>
@@ -5274,7 +5275,7 @@
         <v>許燕輝.jpg</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" ht="15.6">
       <c r="A164" s="3">
         <v>160</v>
       </c>
@@ -5292,7 +5293,7 @@
       </c>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" ht="15.6">
       <c r="A165" s="3">
         <v>161</v>
       </c>
@@ -5313,7 +5314,7 @@
         <v>郭永隆.jpg</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" ht="15.6">
       <c r="A166" s="3">
         <v>162</v>
       </c>
@@ -5334,7 +5335,7 @@
         <v>郭金堡.jpg</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" ht="15.6">
       <c r="A167" s="3">
         <v>163</v>
       </c>
@@ -5355,7 +5356,7 @@
         <v>陳子芸.jpg</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" ht="15.6">
       <c r="A168" s="3">
         <v>164</v>
       </c>
@@ -5373,7 +5374,7 @@
       </c>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" ht="15.6">
       <c r="A169" s="3">
         <v>165</v>
       </c>
@@ -5391,7 +5392,7 @@
       </c>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" ht="15.6">
       <c r="A170" s="3">
         <v>166</v>
       </c>
@@ -5412,7 +5413,7 @@
         <v>陳天成.jpg</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" ht="15.6">
       <c r="A171" s="3">
         <v>167</v>
       </c>
@@ -5433,7 +5434,7 @@
         <v>陳尤莉.jpg</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" ht="15.6">
       <c r="A172" s="3">
         <v>168</v>
       </c>
@@ -5451,7 +5452,7 @@
       </c>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" ht="15.6">
       <c r="A173" s="3">
         <v>169</v>
       </c>
@@ -5472,7 +5473,7 @@
         <v>陳文顧.jpg</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" ht="15.6">
       <c r="A174" s="3">
         <v>170</v>
       </c>
@@ -5490,7 +5491,7 @@
       </c>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" ht="15.6">
       <c r="A175" s="3">
         <v>171</v>
       </c>
@@ -5511,7 +5512,7 @@
         <v>陳水在.jpg</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" ht="15.6">
       <c r="A176" s="3">
         <v>172</v>
       </c>
@@ -5529,7 +5530,7 @@
       </c>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" ht="15.6">
       <c r="A177" s="3">
         <v>173</v>
       </c>
@@ -5547,7 +5548,7 @@
       </c>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" ht="15.6">
       <c r="A178" s="3">
         <v>174</v>
       </c>
@@ -5565,7 +5566,7 @@
       </c>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" ht="15.6">
       <c r="A179" s="3">
         <v>175</v>
       </c>
@@ -5583,7 +5584,7 @@
       </c>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" ht="15.6">
       <c r="A180" s="3">
         <v>176</v>
       </c>
@@ -5604,7 +5605,7 @@
         <v>陳玉珍.jpg</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" ht="15.6">
       <c r="A181" s="3">
         <v>177</v>
       </c>
@@ -5625,7 +5626,7 @@
         <v>陳仲立.jpg</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" ht="15.6">
       <c r="A182" s="3">
         <v>178</v>
       </c>
@@ -5646,7 +5647,7 @@
         <v>陳向鑫.jpg</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" ht="15.6">
       <c r="A183" s="3">
         <v>179</v>
       </c>
@@ -5665,7 +5666,7 @@
         <v>陳成勇.jpg</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" ht="15.6">
       <c r="A184" s="3">
         <v>180</v>
       </c>
@@ -5686,7 +5687,7 @@
         <v>陳成泉.jpg</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" ht="15.6">
       <c r="A185" s="3">
         <v>181</v>
       </c>
@@ -5707,7 +5708,7 @@
         <v>陳孝融.jpg</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" ht="15.6">
       <c r="A186" s="3">
         <v>182</v>
       </c>
@@ -5723,7 +5724,7 @@
       <c r="E186" s="5"/>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" ht="15.6">
       <c r="A187" s="3">
         <v>183</v>
       </c>
@@ -5744,7 +5745,7 @@
         <v>陳志斌.jpg</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" ht="15.6">
       <c r="A188" s="3">
         <v>184</v>
       </c>
@@ -5765,7 +5766,7 @@
         <v>陳志龍.jpg</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" ht="15.6">
       <c r="A189" s="3">
         <v>185</v>
       </c>
@@ -5786,7 +5787,7 @@
         <v>陳秀治.jpg</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" ht="15.6">
       <c r="A190" s="3">
         <v>186</v>
       </c>
@@ -5807,7 +5808,7 @@
         <v>陳秀金.jpg</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" ht="15.6">
       <c r="A191" s="3">
         <v>187</v>
       </c>
@@ -5828,7 +5829,7 @@
         <v>陳秀卿.jpg</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" ht="15.6">
       <c r="A192" s="3">
         <v>188</v>
       </c>
@@ -5849,7 +5850,7 @@
         <v>陳其德.jpg</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" ht="15.6">
       <c r="A193" s="3">
         <v>189</v>
       </c>
@@ -5867,7 +5868,7 @@
       </c>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" ht="15.6">
       <c r="A194" s="3">
         <v>192</v>
       </c>
@@ -5888,7 +5889,7 @@
         <v>陳怡利.jpg</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" ht="15.6">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -5909,7 +5910,7 @@
         <v>陳衍利.jpg</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" ht="15.6">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -5928,7 +5929,7 @@
         <v>陳昆第.jpg</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" ht="15.6">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -5949,7 +5950,7 @@
         <v>陳泱瑚.jpg</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" ht="15.6">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -5967,7 +5968,7 @@
       </c>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" ht="15.6">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -5983,7 +5984,7 @@
       <c r="E199" s="5"/>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" ht="15.6">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -6004,7 +6005,7 @@
         <v>陳威彰.jpg</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" ht="15.6">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -6022,7 +6023,7 @@
       </c>
       <c r="F201" s="3"/>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" ht="15.6">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -6040,7 +6041,7 @@
       </c>
       <c r="F202" s="3"/>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" ht="15.6">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -6061,7 +6062,7 @@
         <v>陳苗生.jpg</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" ht="15.6">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -6082,7 +6083,7 @@
         <v>陳家揚.jpg</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" ht="15.6">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -6100,7 +6101,7 @@
       </c>
       <c r="F205" s="3"/>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" ht="15.6">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -6118,7 +6119,7 @@
       </c>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" ht="15.6">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -6139,7 +6140,7 @@
         <v>陳淑亭.jpg</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" ht="15.6">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -6157,7 +6158,7 @@
       </c>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" ht="15.6">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -6178,7 +6179,7 @@
         <v>陳清寶.jpg</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" ht="15.6">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -6196,7 +6197,7 @@
       </c>
       <c r="F210" s="3"/>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" ht="15.6">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -6217,7 +6218,7 @@
         <v>陳滄江.jpg</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" ht="15.6">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>陳福海.jpg</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" ht="15.6">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -6259,7 +6260,7 @@
         <v>陳德輝.jpg</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" ht="15.6">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -6277,7 +6278,7 @@
       </c>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" ht="15.6">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -6316,7 +6317,7 @@
         <v>陳興坵.jpg</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" ht="15.6">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -6332,7 +6333,7 @@
       <c r="E217" s="5"/>
       <c r="F217" s="3"/>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" ht="15.6">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -6350,7 +6351,7 @@
       </c>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" ht="15.6">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>陳錦偉.jpg</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" ht="15.6">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -6389,7 +6390,7 @@
       </c>
       <c r="F220" s="3"/>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" ht="15.6">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -6407,7 +6408,7 @@
       </c>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" ht="15.6">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -6425,7 +6426,7 @@
       </c>
       <c r="F222" s="3"/>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" ht="15.6">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -6446,7 +6447,7 @@
         <v>程耀德.jpg</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" ht="15.6">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -6467,7 +6468,7 @@
         <v>黃子誠.jpg</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" ht="15.6">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -6488,7 +6489,7 @@
         <v>黃文欣.jpg</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" ht="15.6">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -6509,7 +6510,7 @@
         <v>黃文麟.jpg</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" ht="15.6">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -6525,7 +6526,7 @@
       <c r="E227" s="5"/>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" ht="15.6">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -6543,7 +6544,7 @@
       </c>
       <c r="F228" s="3"/>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" ht="15.6">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -6562,7 +6563,7 @@
         <v>黃秀珍.jpg</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" ht="15.6">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -6580,7 +6581,7 @@
       </c>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" ht="15.6">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -6598,7 +6599,7 @@
       </c>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" ht="15.6">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -6614,7 +6615,7 @@
       <c r="E232" s="5"/>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" ht="15.6">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -6630,7 +6631,7 @@
       <c r="E233" s="5"/>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" ht="15.6">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -6651,7 +6652,7 @@
         <v>黃奕焮.jpg</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" ht="15.6">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -6669,7 +6670,7 @@
       </c>
       <c r="F235" s="3"/>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" ht="15.6">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -6685,7 +6686,7 @@
       <c r="E236" s="5"/>
       <c r="F236" s="3"/>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" ht="15.6">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -6703,7 +6704,7 @@
       </c>
       <c r="F237" s="3"/>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" ht="15.6">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -6724,7 +6725,7 @@
         <v>黃聰成.jpg</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" ht="15.6">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>楊水信.jpg</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" ht="15.6">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -6766,7 +6767,7 @@
         <v>楊永立.jpg</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" ht="15.6">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -6782,7 +6783,7 @@
       </c>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" ht="15.6">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -6798,7 +6799,7 @@
       <c r="E242" s="5"/>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" ht="15.6">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -6819,7 +6820,7 @@
         <v>楊育菡.jpg</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" ht="15.6">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -6840,7 +6841,7 @@
         <v>楊忠俊.jpg</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" ht="15.6">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -6858,7 +6859,7 @@
       </c>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" ht="15.6">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -6874,7 +6875,7 @@
       <c r="E246" s="5"/>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" ht="15.6">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -6892,7 +6893,7 @@
       </c>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" ht="15.6">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -6910,7 +6911,7 @@
       </c>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" ht="15.6">
       <c r="A249" s="3">
         <v>246</v>
       </c>
@@ -6928,7 +6929,7 @@
       </c>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" ht="15.6">
       <c r="A250" s="3">
         <v>247</v>
       </c>
@@ -6949,7 +6950,7 @@
         <v>楊肅元.jpg</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" ht="15.6">
       <c r="A251" s="3">
         <v>248</v>
       </c>
@@ -6970,7 +6971,7 @@
         <v>楊萬山.jpg</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" ht="15.6">
       <c r="A252" s="3">
         <v>249</v>
       </c>
@@ -6991,7 +6992,7 @@
         <v>楊榮祥.jpg</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" ht="15.6">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -7012,7 +7013,7 @@
         <v>楊霈璿.jpg</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" ht="15.6">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -7033,7 +7034,7 @@
         <v>楊應雄.jpg</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" ht="15.6">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -7054,7 +7055,7 @@
         <v>楊鎮浯.jpg</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" ht="15.6">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -7075,7 +7076,7 @@
         <v>楊耀芸.jpg</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" ht="15.6">
       <c r="A257" s="3">
         <v>254</v>
       </c>
@@ -7093,7 +7094,7 @@
       </c>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" ht="15.6">
       <c r="A258" s="3">
         <v>255</v>
       </c>
@@ -7114,7 +7115,7 @@
         <v>董森堡.jpg</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" ht="15.6">
       <c r="A259" s="3">
         <v>256</v>
       </c>
@@ -7132,7 +7133,7 @@
       </c>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" ht="15.6">
       <c r="A260" s="3">
         <v>257</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>廖進入.jpg</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" ht="15.6">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -7171,7 +7172,7 @@
       </c>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" ht="15.6">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -7189,7 +7190,7 @@
       </c>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" ht="15.6">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -7207,7 +7208,7 @@
       </c>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" ht="15.6">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -7225,7 +7226,7 @@
       </c>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" ht="15.6">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -7243,7 +7244,7 @@
       </c>
       <c r="F265" s="3"/>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" ht="15.6">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -7264,7 +7265,7 @@
         <v>歐陽彥木.jpg</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" ht="15.6">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -7285,7 +7286,7 @@
         <v>歐陽豪.jpg</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" ht="15.6">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>歐陽儀雄.jpg</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" ht="15.6">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -7327,7 +7328,7 @@
         <v>蔡乃靖.jpg</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" ht="15.6">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -7348,7 +7349,7 @@
         <v>蔡云豪.jpg</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" ht="15.6">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -7364,7 +7365,7 @@
       <c r="E271" s="5"/>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" ht="15.6">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -7385,7 +7386,7 @@
         <v>蔡水游.jpg</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" ht="15.6">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -7403,7 +7404,7 @@
       </c>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" ht="15.6">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -7424,7 +7425,7 @@
         <v>蔡西湖.jpg</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" ht="15.6">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -7445,7 +7446,7 @@
         <v>蔡其賀.jpg</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" ht="15.6">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -7466,7 +7467,7 @@
         <v>蔡其雍.jpg</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" ht="15.6">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -7487,7 +7488,7 @@
         <v>蔡宗儒.jpg</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" ht="15.6">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -7505,7 +7506,7 @@
       </c>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" ht="15.6">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -7526,7 +7527,7 @@
         <v>蔡建偉2.jpg</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" ht="15.6">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>蔡春生.jpg</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" ht="15.6">
       <c r="A281" s="3">
         <v>278</v>
       </c>
@@ -7568,7 +7569,7 @@
         <v>蔡是民.jpg</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" ht="15.6">
       <c r="A282" s="3">
         <v>279</v>
       </c>
@@ -7586,7 +7587,7 @@
       </c>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" ht="15.6">
       <c r="A283" s="3">
         <v>280</v>
       </c>
@@ -7607,7 +7608,7 @@
         <v>蔡培榮.jpg</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" ht="15.6">
       <c r="A284" s="3">
         <v>281</v>
       </c>
@@ -7628,7 +7629,7 @@
         <v>蔡連進.jpg</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" ht="15.6">
       <c r="A285" s="3">
         <v>282</v>
       </c>
@@ -7646,7 +7647,7 @@
       </c>
       <c r="F285" s="3"/>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" ht="15.6">
       <c r="A286" s="3">
         <v>283</v>
       </c>
@@ -7664,7 +7665,7 @@
       </c>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" ht="15.6">
       <c r="A287" s="3">
         <v>284</v>
       </c>
@@ -7680,7 +7681,7 @@
       <c r="E287" s="5"/>
       <c r="F287" s="3"/>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" ht="15.6">
       <c r="A288" s="3">
         <v>285</v>
       </c>
@@ -7696,7 +7697,7 @@
       <c r="E288" s="5"/>
       <c r="F288" s="3"/>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" ht="15.6">
       <c r="A289" s="3">
         <v>286</v>
       </c>
@@ -7714,7 +7715,7 @@
       </c>
       <c r="F289" s="3"/>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" ht="15.6">
       <c r="A290" s="3">
         <v>287</v>
       </c>
@@ -7735,7 +7736,7 @@
         <v>蔡寶愛.jpg</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:6" ht="15.6">
       <c r="A291" s="3">
         <v>288</v>
       </c>
@@ -7753,7 +7754,7 @@
       </c>
       <c r="F291" s="3"/>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" ht="15.6">
       <c r="A292" s="3">
         <v>289</v>
       </c>
@@ -7771,7 +7772,7 @@
       </c>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" ht="15.6">
       <c r="A293" s="3">
         <v>290</v>
       </c>
@@ -7790,7 +7791,7 @@
         <v>鄭志軍.jpg</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" ht="15.6">
       <c r="A294" s="3">
         <v>291</v>
       </c>
@@ -7811,7 +7812,7 @@
         <v>盧月香.jpg</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:6" ht="15.6">
       <c r="A295" s="3">
         <v>292</v>
       </c>
@@ -7827,7 +7828,7 @@
       <c r="E295" s="5"/>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" ht="15.6">
       <c r="A296" s="3">
         <v>293</v>
       </c>
@@ -7848,7 +7849,7 @@
         <v>盧冠宇.jpg</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" ht="15.6">
       <c r="A297" s="3">
         <v>294</v>
       </c>
@@ -7866,7 +7867,7 @@
       </c>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" ht="15.6">
       <c r="A298" s="3">
         <v>294</v>
       </c>
@@ -7884,7 +7885,7 @@
       </c>
       <c r="F298" s="3"/>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" ht="15.6">
       <c r="A299" s="3">
         <v>295</v>
       </c>
@@ -7902,7 +7903,7 @@
       </c>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" spans="1:6">
+    <row r="300" spans="1:6" ht="15.6">
       <c r="A300" s="3">
         <v>296</v>
       </c>
@@ -7923,7 +7924,7 @@
         <v>謝東龍.jpg</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" ht="15.6">
       <c r="A301" s="3">
         <v>297</v>
       </c>
@@ -7941,7 +7942,7 @@
       </c>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" spans="1:6">
+    <row r="302" spans="1:6" ht="15.6">
       <c r="A302" s="3">
         <v>298</v>
       </c>
@@ -7962,7 +7963,7 @@
         <v>鍾尚志.jpg</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:6" ht="15.6">
       <c r="A303" s="3">
         <v>299</v>
       </c>
@@ -7978,7 +7979,7 @@
       <c r="E303" s="5"/>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:6" ht="15.6">
       <c r="A304" s="3">
         <v>300</v>
       </c>
@@ -7996,7 +7997,7 @@
       </c>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" ht="15.6">
       <c r="A305" s="3">
         <v>301</v>
       </c>
@@ -8017,7 +8018,7 @@
         <v>蘇碧浯.jpg</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" ht="15.6">
       <c r="A306" s="3">
         <v>302</v>
       </c>
@@ -8035,7 +8036,7 @@
       </c>
       <c r="F306" s="3"/>
     </row>
-    <row r="307" spans="1:6">
+    <row r="307" spans="1:6" ht="15.6">
       <c r="A307" s="3">
         <v>303</v>
       </c>
@@ -8056,7 +8057,7 @@
         <v>洪嘉莉.jpg</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
+    <row r="308" spans="1:6" ht="15.6">
       <c r="A308" s="3">
         <v>304</v>
       </c>
@@ -8074,7 +8075,7 @@
       </c>
       <c r="F308" s="3"/>
     </row>
-    <row r="309" spans="1:6">
+    <row r="309" spans="1:6" ht="15.6">
       <c r="A309" s="3">
         <v>305</v>
       </c>
@@ -8092,7 +8093,7 @@
       </c>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" spans="1:6">
+    <row r="310" spans="1:6" ht="15.6">
       <c r="A310" s="3">
         <v>306</v>
       </c>
@@ -8113,7 +8114,7 @@
         <v>張含麗.jpg</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" ht="15.6">
       <c r="A311" s="3">
         <v>307</v>
       </c>
@@ -8131,7 +8132,7 @@
       </c>
       <c r="F311" s="3"/>
     </row>
-    <row r="312" spans="1:6">
+    <row r="312" spans="1:6" ht="15.6">
       <c r="A312" s="3">
         <v>308</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>陳國琍.jpg</v>
       </c>
     </row>
-    <row r="313" spans="1:6">
+    <row r="313" spans="1:6" ht="15.6">
       <c r="A313" s="3">
         <v>309</v>
       </c>
@@ -8170,7 +8171,7 @@
       </c>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" spans="1:6">
+    <row r="314" spans="1:6" ht="15.6">
       <c r="A314" s="3">
         <v>310</v>
       </c>
@@ -8188,7 +8189,7 @@
       </c>
       <c r="F314" s="3"/>
     </row>
-    <row r="315" spans="1:6">
+    <row r="315" spans="1:6" ht="15.6">
       <c r="A315" s="3">
         <v>311</v>
       </c>
@@ -8206,7 +8207,7 @@
       </c>
       <c r="F315" s="3"/>
     </row>
-    <row r="316" spans="1:6">
+    <row r="316" spans="1:6" ht="15.6">
       <c r="A316" s="3">
         <v>312</v>
       </c>
@@ -8224,7 +8225,7 @@
       </c>
       <c r="F316" s="3"/>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" ht="15.6">
       <c r="A317" s="3">
         <v>313</v>
       </c>
@@ -8242,7 +8243,7 @@
       </c>
       <c r="F317" s="3"/>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" ht="15.6">
       <c r="A318" s="3">
         <v>314</v>
       </c>
@@ -8260,7 +8261,7 @@
       </c>
       <c r="F318" s="3"/>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" ht="15.6">
       <c r="A319" s="3">
         <v>315</v>
       </c>
@@ -8281,7 +8282,7 @@
         <v>蔡建立.jpg</v>
       </c>
     </row>
-    <row r="320" spans="1:6">
+    <row r="320" spans="1:6" ht="15.6">
       <c r="A320" s="3">
         <v>316</v>
       </c>
@@ -8302,7 +8303,7 @@
         <v>陳水德.jpg</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" ht="15.6">
       <c r="A321" s="3">
         <v>317</v>
       </c>
@@ -8320,7 +8321,7 @@
       </c>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" ht="15.6">
       <c r="A322" s="3">
         <v>318</v>
       </c>
@@ -8341,7 +8342,7 @@
         <v>周根在.jpg</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:6" ht="15.6">
       <c r="A323" s="3">
         <v>319</v>
       </c>
@@ -8362,7 +8363,7 @@
         <v>李琳瑯.jpg</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:6" ht="15.6">
       <c r="A324" s="3">
         <v>320</v>
       </c>
@@ -8380,7 +8381,7 @@
       </c>
       <c r="F324" s="3"/>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" ht="15.6">
       <c r="A325" s="3">
         <v>321</v>
       </c>
@@ -8401,7 +8402,7 @@
         <v>方水萬.jpg</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:6" ht="15.6">
       <c r="A326" s="3">
         <v>322</v>
       </c>
@@ -8422,7 +8423,7 @@
         <v>蔡金照.jpg</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:6" ht="15.6">
       <c r="A327" s="3">
         <v>323</v>
       </c>
@@ -8438,7 +8439,7 @@
       <c r="E327" s="5"/>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:6" ht="15.6">
       <c r="A328" s="3">
         <v>324</v>
       </c>
@@ -8454,7 +8455,7 @@
       <c r="E328" s="5"/>
       <c r="F328" s="3"/>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:6" ht="15.6">
       <c r="A329" s="3">
         <v>325</v>
       </c>
@@ -8470,7 +8471,7 @@
       <c r="E329" s="5"/>
       <c r="F329" s="3"/>
     </row>
-    <row r="330" spans="1:6">
+    <row r="330" spans="1:6" ht="15.6">
       <c r="A330" s="3">
         <v>326</v>
       </c>
@@ -8484,7 +8485,7 @@
       <c r="E330" s="5"/>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:6" ht="15.6">
       <c r="A331" s="3">
         <v>327</v>
       </c>
@@ -8498,7 +8499,7 @@
       <c r="E331" s="5"/>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:6" ht="15.6">
       <c r="A332" s="3">
         <v>328</v>
       </c>
@@ -8516,7 +8517,7 @@
       </c>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:6" ht="15.6">
       <c r="A333" s="3">
         <v>329</v>
       </c>
@@ -8530,7 +8531,7 @@
       <c r="E333" s="5"/>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" spans="1:6">
+    <row r="334" spans="1:6" ht="15.6">
       <c r="A334" s="3">
         <v>330</v>
       </c>
@@ -8544,7 +8545,7 @@
       <c r="E334" s="5"/>
       <c r="F334" s="3"/>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:6" ht="15.6">
       <c r="A335" s="3">
         <v>331</v>
       </c>
@@ -8558,7 +8559,7 @@
       <c r="E335" s="5"/>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:6" ht="15.6">
       <c r="A336" s="3">
         <v>332</v>
       </c>
@@ -8574,7 +8575,7 @@
       <c r="E336" s="5"/>
       <c r="F336" s="3"/>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:6" ht="15.6">
       <c r="A337" s="3">
         <v>333</v>
       </c>
@@ -8590,7 +8591,7 @@
       <c r="E337" s="5"/>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" spans="1:6">
+    <row r="338" spans="1:6" ht="15.6">
       <c r="A338" s="3">
         <v>334</v>
       </c>
@@ -8606,7 +8607,7 @@
       <c r="E338" s="5"/>
       <c r="F338" s="3"/>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:6" ht="15.6">
       <c r="A339" s="3">
         <v>335</v>
       </c>
@@ -8627,7 +8628,7 @@
         <v>李玉葉.jpg</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:6" ht="15.6">
       <c r="A340" s="3">
         <v>336</v>
       </c>
@@ -8643,7 +8644,7 @@
       <c r="E340" s="5"/>
       <c r="F340" s="3"/>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:6" ht="15.6">
       <c r="A341" s="3">
         <v>337</v>
       </c>
@@ -8659,7 +8660,7 @@
       <c r="E341" s="5"/>
       <c r="F341" s="3"/>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:6" ht="15.6">
       <c r="A342" s="3">
         <v>338</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>翁根龍.jpg</v>
       </c>
     </row>
-    <row r="343" spans="1:6">
+    <row r="343" spans="1:6" ht="15.6">
       <c r="A343" s="3">
         <v>339</v>
       </c>
@@ -8694,7 +8695,7 @@
       <c r="E343" s="5"/>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:6" ht="15.6">
       <c r="A344" s="3">
         <v>340</v>
       </c>
@@ -8712,7 +8713,7 @@
       </c>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:6" ht="15.6">
       <c r="A345" s="3">
         <v>341</v>
       </c>
@@ -8728,7 +8729,7 @@
       <c r="E345" s="5"/>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:6" ht="15.6">
       <c r="A346" s="3">
         <v>342</v>
       </c>
@@ -8746,7 +8747,7 @@
       </c>
       <c r="F346" s="3"/>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:6" ht="15.6">
       <c r="A347" s="3">
         <v>343</v>
       </c>
@@ -8764,7 +8765,7 @@
       </c>
       <c r="F347" s="3"/>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:6" ht="15.6">
       <c r="A348" s="3">
         <v>344</v>
       </c>
@@ -8783,7 +8784,7 @@
         <v>謝鴻儒.jpg</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:6" ht="15.6">
       <c r="A349" s="3">
         <v>345</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>關志武.jpg</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:6" ht="15.6">
       <c r="A350" s="3">
         <v>346</v>
       </c>
@@ -8823,7 +8824,7 @@
         <v>呂瑞泰.jpg</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:6" ht="15.6">
       <c r="A351" s="3">
         <v>347</v>
       </c>
@@ -8844,7 +8845,7 @@
         <v>李開陣.jpg</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:6" ht="15.6">
       <c r="A352" s="3">
         <v>348</v>
       </c>
@@ -8863,7 +8864,7 @@
         <v>林金月.jpg</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:6" ht="15.6">
       <c r="A353" s="3">
         <v>349</v>
       </c>
@@ -8881,7 +8882,7 @@
       </c>
       <c r="F353" s="3"/>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:6" ht="15.6">
       <c r="A354" s="3">
         <v>350</v>
       </c>
@@ -8897,7 +8898,7 @@
       <c r="E354" s="5"/>
       <c r="F354" s="3"/>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:6" ht="15.6">
       <c r="A355" s="3">
         <v>351</v>
       </c>
@@ -8915,7 +8916,7 @@
       </c>
       <c r="F355" s="3"/>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:6" ht="15.6">
       <c r="A356" s="3">
         <v>352</v>
       </c>
@@ -8931,7 +8932,7 @@
       <c r="E356" s="5"/>
       <c r="F356" s="3"/>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:6" ht="15.6">
       <c r="A357" s="3">
         <v>353</v>
       </c>
@@ -8952,7 +8953,7 @@
         <v>許績才.jpg</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:6" ht="15.6">
       <c r="A358" s="3">
         <v>354</v>
       </c>
@@ -8968,7 +8969,7 @@
       <c r="E358" s="5"/>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:6" ht="15.6">
       <c r="A359" s="3">
         <v>355</v>
       </c>
@@ -8984,7 +8985,7 @@
       <c r="E359" s="5"/>
       <c r="F359" s="3"/>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:6" ht="15.6">
       <c r="A360" s="3">
         <v>356</v>
       </c>
@@ -9000,7 +9001,7 @@
       <c r="E360" s="5"/>
       <c r="F360" s="3"/>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:6" ht="15.6">
       <c r="A361" s="3">
         <v>357</v>
       </c>
@@ -9016,7 +9017,7 @@
       <c r="E361" s="5"/>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:6" ht="15.6">
       <c r="A362" s="3">
         <v>358</v>
       </c>
@@ -9032,7 +9033,7 @@
       <c r="E362" s="5"/>
       <c r="F362" s="3"/>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:6" ht="15.6">
       <c r="A363" s="3">
         <v>359</v>
       </c>
@@ -9048,7 +9049,7 @@
       <c r="E363" s="5"/>
       <c r="F363" s="3"/>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:6" ht="15.6">
       <c r="A364" s="3">
         <v>360</v>
       </c>
@@ -9064,7 +9065,7 @@
       <c r="E364" s="5"/>
       <c r="F364" s="3"/>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:6" ht="15.6">
       <c r="A365" s="3">
         <v>361</v>
       </c>
@@ -9083,7 +9084,7 @@
         <v>蔡其明.jpg</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:6" ht="15.6">
       <c r="A366" s="3">
         <v>362</v>
       </c>
@@ -9099,7 +9100,7 @@
       <c r="E366" s="5"/>
       <c r="F366" s="3"/>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:6" ht="15.6">
       <c r="A367" s="3">
         <v>363</v>
       </c>
@@ -9115,7 +9116,7 @@
       <c r="E367" s="5"/>
       <c r="F367" s="3"/>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:6" ht="15.6">
       <c r="A368" s="3">
         <v>364</v>
       </c>
@@ -9131,7 +9132,7 @@
       <c r="E368" s="5"/>
       <c r="F368" s="3"/>
     </row>
-    <row r="369" spans="1:6">
+    <row r="369" spans="1:6" ht="15.6">
       <c r="A369" s="3">
         <v>365</v>
       </c>
@@ -9150,7 +9151,7 @@
         <v>蔡怡萱.jpg</v>
       </c>
     </row>
-    <row r="370" spans="1:6">
+    <row r="370" spans="1:6" ht="15.6">
       <c r="A370" s="3">
         <v>366</v>
       </c>
@@ -9166,7 +9167,7 @@
       <c r="E370" s="5"/>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" spans="1:6">
+    <row r="371" spans="1:6" ht="15.6">
       <c r="A371" s="3">
         <v>367</v>
       </c>
@@ -9182,7 +9183,7 @@
       <c r="E371" s="5"/>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" spans="1:6">
+    <row r="372" spans="1:6" ht="15.6">
       <c r="A372" s="3">
         <v>368</v>
       </c>
@@ -9198,7 +9199,7 @@
       <c r="E372" s="5"/>
       <c r="F372" s="3"/>
     </row>
-    <row r="373" spans="1:6">
+    <row r="373" spans="1:6" ht="15.6">
       <c r="A373" s="3">
         <v>369</v>
       </c>
@@ -9216,7 +9217,7 @@
       </c>
       <c r="F373" s="3"/>
     </row>
-    <row r="374" spans="1:6">
+    <row r="374" spans="1:6" ht="15.6">
       <c r="A374" s="3">
         <v>370</v>
       </c>
@@ -9232,7 +9233,7 @@
       <c r="E374" s="5"/>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" spans="1:6">
+    <row r="375" spans="1:6" ht="15.6">
       <c r="A375" s="3">
         <v>371</v>
       </c>
@@ -9251,7 +9252,7 @@
         <v>蔡金爵.jpg</v>
       </c>
     </row>
-    <row r="376" spans="1:6">
+    <row r="376" spans="1:6" ht="15.6">
       <c r="A376" s="3">
         <v>372</v>
       </c>
@@ -9270,7 +9271,7 @@
         <v>蔡祥坤.jpg</v>
       </c>
     </row>
-    <row r="377" spans="1:6">
+    <row r="377" spans="1:6" ht="15.6">
       <c r="A377" s="3">
         <v>373</v>
       </c>
@@ -9289,7 +9290,7 @@
         <v>周偉義.jpg</v>
       </c>
     </row>
-    <row r="378" spans="1:6">
+    <row r="378" spans="1:6" ht="15.6">
       <c r="A378" s="3">
         <v>374</v>
       </c>
@@ -9303,9 +9304,12 @@
         <v>1985</v>
       </c>
       <c r="E378" s="5"/>
-      <c r="F378" s="3"/>
-    </row>
-    <row r="379" spans="1:6">
+      <c r="F378" s="3" t="str">
+        <f>B378&amp;".jpg"</f>
+        <v>許程勛.jpg</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" ht="15.6">
       <c r="A379" s="3">
         <v>375</v>
       </c>
@@ -9326,7 +9330,7 @@
         <v>楊雨川.jpg</v>
       </c>
     </row>
-    <row r="380" spans="1:6">
+    <row r="380" spans="1:6" ht="15.6">
       <c r="A380" s="3">
         <v>376</v>
       </c>
@@ -9347,7 +9351,7 @@
         <v>鄭易岳.jpg</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:6" ht="15.6">
       <c r="A381" s="3">
         <v>377</v>
       </c>
@@ -9363,7 +9367,7 @@
       <c r="E381" s="5"/>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:6" ht="15.6">
       <c r="A382" s="3">
         <v>378</v>
       </c>
@@ -9379,7 +9383,7 @@
       <c r="E382" s="5"/>
       <c r="F382" s="3"/>
     </row>
-    <row r="383" spans="1:6">
+    <row r="383" spans="1:6" ht="15.6">
       <c r="A383" s="3">
         <v>379</v>
       </c>
@@ -9400,7 +9404,7 @@
         <v>辛文進.jpg</v>
       </c>
     </row>
-    <row r="384" spans="1:6">
+    <row r="384" spans="1:6" ht="15.6">
       <c r="A384" s="3">
         <v>380</v>
       </c>
@@ -9416,7 +9420,7 @@
       <c r="E384" s="5"/>
       <c r="F384" s="3"/>
     </row>
-    <row r="385" spans="1:6">
+    <row r="385" spans="1:6" ht="15.6">
       <c r="A385" s="3">
         <v>381</v>
       </c>
@@ -9437,7 +9441,7 @@
         <v>黃延良.jpg</v>
       </c>
     </row>
-    <row r="386" spans="1:6">
+    <row r="386" spans="1:6" ht="15.6">
       <c r="A386" s="3">
         <v>382</v>
       </c>
@@ -9453,7 +9457,7 @@
       <c r="E386" s="5"/>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" spans="1:6">
+    <row r="387" spans="1:6" ht="15.6">
       <c r="A387" s="3">
         <v>383</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>戴德強.jpg</v>
       </c>
     </row>
-    <row r="388" spans="1:6">
+    <row r="388" spans="1:6" ht="15.6">
       <c r="A388" s="3">
         <v>384</v>
       </c>
@@ -9495,7 +9499,7 @@
         <v>顏士強.jpg</v>
       </c>
     </row>
-    <row r="389" spans="1:6">
+    <row r="389" spans="1:6" ht="15.6">
       <c r="A389" s="3">
         <v>385</v>
       </c>
@@ -9511,7 +9515,7 @@
       <c r="E389" s="5"/>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" spans="1:6">
+    <row r="390" spans="1:6" ht="15.6">
       <c r="A390" s="3">
         <v>386</v>
       </c>
@@ -9532,7 +9536,7 @@
         <v>張瀚龍.jpg</v>
       </c>
     </row>
-    <row r="391" spans="1:6">
+    <row r="391" spans="1:6" ht="15.6">
       <c r="A391" s="3">
         <v>387</v>
       </c>
@@ -9550,7 +9554,7 @@
       </c>
       <c r="F391" s="3"/>
     </row>
-    <row r="392" spans="1:6">
+    <row r="392" spans="1:6" ht="15.6">
       <c r="A392" s="3">
         <v>388</v>
       </c>
@@ -9571,7 +9575,7 @@
         <v>陳賜發.jpg</v>
       </c>
     </row>
-    <row r="393" spans="1:6">
+    <row r="393" spans="1:6" ht="15.6">
       <c r="A393" s="3">
         <v>389</v>
       </c>
@@ -9589,7 +9593,7 @@
       </c>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" spans="1:6">
+    <row r="394" spans="1:6" ht="15.6">
       <c r="A394" s="3">
         <v>390</v>
       </c>
@@ -9607,7 +9611,7 @@
       </c>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" spans="1:6">
+    <row r="395" spans="1:6" ht="15.6">
       <c r="A395" s="3">
         <v>391</v>
       </c>
@@ -9625,7 +9629,7 @@
       </c>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" spans="1:6">
+    <row r="396" spans="1:6" ht="15.6">
       <c r="A396" s="3">
         <v>392</v>
       </c>
@@ -9643,7 +9647,7 @@
       </c>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" spans="1:6">
+    <row r="397" spans="1:6" ht="15.6">
       <c r="A397" s="3">
         <v>393</v>
       </c>
@@ -9661,7 +9665,7 @@
       </c>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" spans="1:6">
+    <row r="398" spans="1:6" ht="15.6">
       <c r="A398" s="3">
         <v>394</v>
       </c>
@@ -9682,7 +9686,7 @@
         <v>陳文傑.jpg</v>
       </c>
     </row>
-    <row r="399" spans="1:6">
+    <row r="399" spans="1:6" ht="15.6">
       <c r="A399" s="3">
         <v>395</v>
       </c>
@@ -9703,7 +9707,7 @@
         <v>陳福林.jpg</v>
       </c>
     </row>
-    <row r="400" spans="1:6">
+    <row r="400" spans="1:6" ht="15.6">
       <c r="A400" s="3">
         <v>396</v>
       </c>
@@ -9721,7 +9725,7 @@
       </c>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" spans="1:6">
+    <row r="401" spans="1:6" ht="15.6">
       <c r="A401" s="3">
         <v>397</v>
       </c>
@@ -9742,7 +9746,7 @@
         <v>黃添丁.jpg</v>
       </c>
     </row>
-    <row r="402" spans="1:6">
+    <row r="402" spans="1:6" ht="15.6">
       <c r="A402" s="3">
         <v>398</v>
       </c>
@@ -9760,7 +9764,7 @@
       </c>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:6" ht="15.6">
       <c r="A403" s="3">
         <v>399</v>
       </c>
@@ -9781,7 +9785,7 @@
         <v>黃志明.jpg</v>
       </c>
     </row>
-    <row r="404" spans="1:6">
+    <row r="404" spans="1:6" ht="15.6">
       <c r="A404" s="3">
         <v>400</v>
       </c>
@@ -9802,7 +9806,7 @@
         <v>楊恭勤.jpg</v>
       </c>
     </row>
-    <row r="405" spans="1:6">
+    <row r="405" spans="1:6" ht="15.6">
       <c r="A405" s="3">
         <v>401</v>
       </c>
@@ -9823,7 +9827,7 @@
         <v>周家才.jpg</v>
       </c>
     </row>
-    <row r="406" spans="1:6">
+    <row r="406" spans="1:6" ht="15.6">
       <c r="A406" s="3">
         <v>402</v>
       </c>
@@ -9841,7 +9845,7 @@
       </c>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" spans="1:6">
+    <row r="407" spans="1:6" ht="15.6">
       <c r="A407" s="3">
         <v>403</v>
       </c>
@@ -9859,7 +9863,7 @@
       </c>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" spans="1:6">
+    <row r="408" spans="1:6" ht="15.6">
       <c r="A408" s="3">
         <v>404</v>
       </c>
@@ -9880,7 +9884,7 @@
         <v>吳孟霖.jpg</v>
       </c>
     </row>
-    <row r="409" spans="1:6">
+    <row r="409" spans="1:6" ht="15.6">
       <c r="A409" s="3">
         <v>405</v>
       </c>
@@ -9901,7 +9905,7 @@
         <v>陳晚開.jpg</v>
       </c>
     </row>
-    <row r="410" spans="1:6">
+    <row r="410" spans="1:6" ht="15.6">
       <c r="A410" s="3">
         <v>406</v>
       </c>
@@ -9919,7 +9923,7 @@
       </c>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" spans="1:6">
+    <row r="411" spans="1:6" ht="15.6">
       <c r="A411" s="3">
         <v>407</v>
       </c>
@@ -9940,7 +9944,7 @@
         <v>陳偃武.jpg</v>
       </c>
     </row>
-    <row r="412" spans="1:6">
+    <row r="412" spans="1:6" ht="15.6">
       <c r="A412" s="3">
         <v>408</v>
       </c>
@@ -9961,7 +9965,7 @@
         <v>謝慶閣.jpg</v>
       </c>
     </row>
-    <row r="413" spans="1:6">
+    <row r="413" spans="1:6" ht="15.6">
       <c r="A413" s="3">
         <v>409</v>
       </c>
@@ -9979,7 +9983,7 @@
       </c>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" spans="1:6">
+    <row r="414" spans="1:6" ht="15.6">
       <c r="A414" s="3">
         <v>410</v>
       </c>
@@ -10000,7 +10004,7 @@
         <v>蔡懷芝.jpg</v>
       </c>
     </row>
-    <row r="415" spans="1:6">
+    <row r="415" spans="1:6" ht="15.6">
       <c r="A415" s="3">
         <v>411</v>
       </c>
@@ -10021,7 +10025,7 @@
         <v>陳錦章.jpg</v>
       </c>
     </row>
-    <row r="416" spans="1:6">
+    <row r="416" spans="1:6" ht="15.6">
       <c r="A416" s="3">
         <v>412</v>
       </c>
@@ -10039,7 +10043,7 @@
       </c>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" spans="1:6">
+    <row r="417" spans="1:6" ht="15.6">
       <c r="A417" s="3">
         <v>413</v>
       </c>
@@ -10060,7 +10064,7 @@
         <v>黃建忠.jpg</v>
       </c>
     </row>
-    <row r="418" spans="1:6">
+    <row r="418" spans="1:6" ht="15.6">
       <c r="A418" s="3">
         <v>414</v>
       </c>
@@ -10081,7 +10085,7 @@
         <v>呂永林.jpg</v>
       </c>
     </row>
-    <row r="419" spans="1:6">
+    <row r="419" spans="1:6" ht="15.6">
       <c r="A419" s="3">
         <v>415</v>
       </c>
@@ -10099,7 +10103,7 @@
       </c>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" spans="1:6">
+    <row r="420" spans="1:6" ht="15.6">
       <c r="A420" s="3">
         <v>416</v>
       </c>
@@ -10120,7 +10124,7 @@
         <v>許三進.jpg</v>
       </c>
     </row>
-    <row r="421" spans="1:6">
+    <row r="421" spans="1:6" ht="15.6">
       <c r="A421" s="3">
         <v>417</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>許明吉.jpg</v>
       </c>
     </row>
-    <row r="422" spans="1:6">
+    <row r="422" spans="1:6" ht="15.6">
       <c r="A422" s="3">
         <v>418</v>
       </c>
@@ -10162,7 +10166,7 @@
         <v>楊振嵩.jpg</v>
       </c>
     </row>
-    <row r="423" spans="1:6">
+    <row r="423" spans="1:6" ht="15.6">
       <c r="A423" s="3">
         <v>419</v>
       </c>
@@ -10183,7 +10187,7 @@
         <v>楊龍傳.jpg</v>
       </c>
     </row>
-    <row r="424" spans="1:6">
+    <row r="424" spans="1:6" ht="15.6">
       <c r="A424" s="3">
         <v>420</v>
       </c>
@@ -10204,7 +10208,7 @@
         <v>翁明海.jpg</v>
       </c>
     </row>
-    <row r="425" spans="1:6">
+    <row r="425" spans="1:6" ht="15.6">
       <c r="A425" s="3">
         <v>421</v>
       </c>
@@ -10225,7 +10229,7 @@
         <v>翁品洋.jpg</v>
       </c>
     </row>
-    <row r="426" spans="1:6">
+    <row r="426" spans="1:6" ht="15.6">
       <c r="A426" s="3">
         <v>422</v>
       </c>
@@ -10246,7 +10250,7 @@
         <v>洪天南.jpg</v>
       </c>
     </row>
-    <row r="427" spans="1:6">
+    <row r="427" spans="1:6" ht="15.6">
       <c r="A427" s="3">
         <v>423</v>
       </c>
@@ -10264,7 +10268,7 @@
       </c>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" spans="1:6">
+    <row r="428" spans="1:6" ht="15.6">
       <c r="A428" s="3">
         <v>424</v>
       </c>
@@ -10285,7 +10289,7 @@
         <v>蔡福榮.jpg</v>
       </c>
     </row>
-    <row r="429" spans="1:6">
+    <row r="429" spans="1:6" ht="15.6">
       <c r="A429" s="3">
         <v>425</v>
       </c>
@@ -10303,7 +10307,7 @@
       </c>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" spans="1:6">
+    <row r="430" spans="1:6" ht="15.6">
       <c r="A430" s="3">
         <v>426</v>
       </c>
@@ -10324,7 +10328,7 @@
         <v>林龍照.jpg</v>
       </c>
     </row>
-    <row r="431" spans="1:6">
+    <row r="431" spans="1:6" ht="15.6">
       <c r="A431" s="3">
         <v>427</v>
       </c>
@@ -10342,7 +10346,7 @@
       </c>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" spans="1:6">
+    <row r="432" spans="1:6" ht="15.6">
       <c r="A432" s="3">
         <v>428</v>
       </c>
@@ -10360,7 +10364,7 @@
       </c>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" spans="1:6">
+    <row r="433" spans="1:6" ht="15.6">
       <c r="A433" s="3">
         <v>429</v>
       </c>
@@ -10378,7 +10382,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="1:6">
+    <row r="434" spans="1:6" ht="15.6">
       <c r="A434" s="3">
         <v>430</v>
       </c>
@@ -10396,7 +10400,7 @@
       </c>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" spans="1:6">
+    <row r="435" spans="1:6" ht="15.6">
       <c r="A435" s="3">
         <v>431</v>
       </c>
@@ -10417,7 +10421,7 @@
         <v>莊金蓮.jpg</v>
       </c>
     </row>
-    <row r="436" spans="1:6">
+    <row r="436" spans="1:6" ht="15.6">
       <c r="A436" s="3">
         <v>432</v>
       </c>
@@ -10435,7 +10439,7 @@
       </c>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" spans="1:6">
+    <row r="437" spans="1:6" ht="15.6">
       <c r="A437" s="3">
         <v>433</v>
       </c>
@@ -10453,7 +10457,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="1:6">
+    <row r="438" spans="1:6" ht="15.6">
       <c r="A438" s="3">
         <v>434</v>
       </c>
@@ -10471,7 +10475,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="1:6">
+    <row r="439" spans="1:6" ht="15.6">
       <c r="A439" s="3">
         <v>435</v>
       </c>
@@ -10489,7 +10493,7 @@
       </c>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" spans="1:6">
+    <row r="440" spans="1:6" ht="15.6">
       <c r="A440" s="3">
         <v>436</v>
       </c>
@@ -10507,7 +10511,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="1:6">
+    <row r="441" spans="1:6" ht="15.6">
       <c r="A441" s="3">
         <v>437</v>
       </c>
@@ -10525,7 +10529,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="1:6">
+    <row r="442" spans="1:6" ht="15.6">
       <c r="A442" s="3">
         <v>438</v>
       </c>
@@ -10543,7 +10547,7 @@
       </c>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" spans="1:6">
+    <row r="443" spans="1:6" ht="15.6">
       <c r="A443" s="3">
         <v>439</v>
       </c>
@@ -10561,7 +10565,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="1:6">
+    <row r="444" spans="1:6" ht="15.6">
       <c r="A444" s="3">
         <v>440</v>
       </c>
@@ -10579,7 +10583,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="1:6">
+    <row r="445" spans="1:6" ht="15.6">
       <c r="A445" s="3">
         <v>441</v>
       </c>
@@ -10597,7 +10601,7 @@
       </c>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" spans="1:6">
+    <row r="446" spans="1:6" ht="15.6">
       <c r="A446" s="3">
         <v>442</v>
       </c>
@@ -10615,7 +10619,7 @@
       </c>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" spans="1:6">
+    <row r="447" spans="1:6" ht="15.6">
       <c r="A447" s="3">
         <v>443</v>
       </c>
@@ -10633,7 +10637,7 @@
       </c>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" spans="1:6">
+    <row r="448" spans="1:6" ht="15.6">
       <c r="A448" s="3">
         <v>444</v>
       </c>
@@ -10654,7 +10658,7 @@
         <v>盧志嶢.jpg</v>
       </c>
     </row>
-    <row r="449" spans="1:6">
+    <row r="449" spans="1:6" ht="15.6">
       <c r="A449" s="3">
         <v>445</v>
       </c>
@@ -10672,7 +10676,7 @@
       </c>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" spans="1:6">
+    <row r="450" spans="1:6" ht="15.6">
       <c r="A450" s="3">
         <v>446</v>
       </c>
@@ -10690,7 +10694,7 @@
       </c>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" spans="1:6">
+    <row r="451" spans="1:6" ht="15.6">
       <c r="A451" s="3">
         <v>447</v>
       </c>
@@ -10708,7 +10712,7 @@
       </c>
       <c r="F451" s="3"/>
     </row>
-    <row r="452" spans="1:6">
+    <row r="452" spans="1:6" ht="15.6">
       <c r="A452" s="3">
         <v>448</v>
       </c>
@@ -10726,7 +10730,7 @@
       </c>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" spans="1:6">
+    <row r="453" spans="1:6" ht="15.6">
       <c r="A453" s="3">
         <v>449</v>
       </c>
@@ -10744,7 +10748,7 @@
       </c>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" spans="1:6">
+    <row r="454" spans="1:6" ht="15.6">
       <c r="A454" s="3">
         <v>450</v>
       </c>
@@ -10762,7 +10766,7 @@
       </c>
       <c r="F454" s="3"/>
     </row>
-    <row r="455" spans="1:6">
+    <row r="455" spans="1:6" ht="15.6">
       <c r="A455" s="3">
         <v>451</v>
       </c>
@@ -10780,7 +10784,7 @@
       </c>
       <c r="F455" s="3"/>
     </row>
-    <row r="456" spans="1:6">
+    <row r="456" spans="1:6" ht="15.6">
       <c r="A456" s="3">
         <v>452</v>
       </c>
@@ -10801,7 +10805,7 @@
         <v>吳志成.jpg</v>
       </c>
     </row>
-    <row r="457" spans="1:6">
+    <row r="457" spans="1:6" ht="15.6">
       <c r="A457" s="3">
         <v>453</v>
       </c>
@@ -10819,7 +10823,7 @@
       </c>
       <c r="F457" s="3"/>
     </row>
-    <row r="458" spans="1:6">
+    <row r="458" spans="1:6" ht="15.6">
       <c r="A458" s="3">
         <v>454</v>
       </c>
@@ -10840,7 +10844,7 @@
         <v>蔡顯明.jpg</v>
       </c>
     </row>
-    <row r="459" spans="1:6">
+    <row r="459" spans="1:6" ht="15.6">
       <c r="A459" s="3">
         <v>455</v>
       </c>
@@ -10858,7 +10862,7 @@
       </c>
       <c r="F459" s="3"/>
     </row>
-    <row r="460" spans="1:6">
+    <row r="460" spans="1:6" ht="15.6">
       <c r="A460" s="3">
         <v>456</v>
       </c>
@@ -10876,7 +10880,7 @@
       </c>
       <c r="F460" s="3"/>
     </row>
-    <row r="461" spans="1:6">
+    <row r="461" spans="1:6" ht="15.6">
       <c r="A461" s="3">
         <v>457</v>
       </c>
@@ -10894,7 +10898,7 @@
       </c>
       <c r="F461" s="3"/>
     </row>
-    <row r="462" spans="1:6">
+    <row r="462" spans="1:6" ht="15.6">
       <c r="A462" s="3">
         <v>458</v>
       </c>
@@ -10912,7 +10916,7 @@
       </c>
       <c r="F462" s="3"/>
     </row>
-    <row r="463" spans="1:6">
+    <row r="463" spans="1:6" ht="15.6">
       <c r="A463" s="3">
         <v>459</v>
       </c>
@@ -10933,7 +10937,7 @@
         <v>呂光河.jpg</v>
       </c>
     </row>
-    <row r="464" spans="1:6">
+    <row r="464" spans="1:6" ht="15.6">
       <c r="A464" s="3">
         <v>460</v>
       </c>
@@ -10951,7 +10955,7 @@
       </c>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" spans="1:6">
+    <row r="465" spans="1:6" ht="15.6">
       <c r="A465" s="3">
         <v>461</v>
       </c>
@@ -10972,7 +10976,7 @@
         <v>李賢慨.jpg</v>
       </c>
     </row>
-    <row r="466" spans="1:6">
+    <row r="466" spans="1:6" ht="15.6">
       <c r="A466" s="3">
         <v>462</v>
       </c>
@@ -10990,7 +10994,7 @@
       </c>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" spans="1:6">
+    <row r="467" spans="1:6" ht="15.6">
       <c r="A467" s="3">
         <v>463</v>
       </c>
@@ -11008,7 +11012,7 @@
       </c>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" spans="1:6">
+    <row r="468" spans="1:6" ht="15.6">
       <c r="A468" s="3">
         <v>464</v>
       </c>
@@ -11026,7 +11030,7 @@
       </c>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" spans="1:6">
+    <row r="469" spans="1:6" ht="15.6">
       <c r="A469" s="3">
         <v>465</v>
       </c>
@@ -11044,7 +11048,7 @@
       </c>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" spans="1:6">
+    <row r="470" spans="1:6" ht="15.6">
       <c r="A470" s="3">
         <v>466</v>
       </c>
@@ -11062,7 +11066,7 @@
       </c>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" spans="1:6">
+    <row r="471" spans="1:6" ht="15.6">
       <c r="A471" s="3">
         <v>467</v>
       </c>
@@ -11080,7 +11084,7 @@
       </c>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" spans="1:6">
+    <row r="472" spans="1:6" ht="15.6">
       <c r="A472" s="3">
         <v>468</v>
       </c>
@@ -11098,7 +11102,7 @@
       </c>
       <c r="F472" s="3"/>
     </row>
-    <row r="473" spans="1:6">
+    <row r="473" spans="1:6" ht="15.6">
       <c r="A473" s="3">
         <v>469</v>
       </c>
@@ -11116,7 +11120,7 @@
       </c>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" spans="1:6">
+    <row r="474" spans="1:6" ht="15.6">
       <c r="A474" s="3">
         <v>470</v>
       </c>
@@ -11134,7 +11138,7 @@
       </c>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" spans="1:6">
+    <row r="475" spans="1:6" ht="15.6">
       <c r="A475" s="3">
         <v>471</v>
       </c>
@@ -11152,7 +11156,7 @@
       </c>
       <c r="F475" s="3"/>
     </row>
-    <row r="476" spans="1:6">
+    <row r="476" spans="1:6" ht="15.6">
       <c r="A476" s="3">
         <v>472</v>
       </c>
@@ -11170,7 +11174,7 @@
       </c>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" spans="1:6">
+    <row r="477" spans="1:6" ht="15.6">
       <c r="A477" s="3">
         <v>473</v>
       </c>
@@ -11191,7 +11195,7 @@
         <v>方耀年.jpg</v>
       </c>
     </row>
-    <row r="478" spans="1:6">
+    <row r="478" spans="1:6" ht="15.6">
       <c r="A478" s="3">
         <v>474</v>
       </c>
@@ -11209,7 +11213,7 @@
       </c>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" spans="1:6">
+    <row r="479" spans="1:6" ht="15.6">
       <c r="A479" s="3">
         <v>475</v>
       </c>
@@ -11227,7 +11231,7 @@
       </c>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" spans="1:6">
+    <row r="480" spans="1:6" ht="15.6">
       <c r="A480" s="3">
         <v>476</v>
       </c>
@@ -11245,7 +11249,7 @@
       </c>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" spans="1:6">
+    <row r="481" spans="1:6" ht="15.6">
       <c r="A481" s="3">
         <v>477</v>
       </c>
@@ -11263,7 +11267,7 @@
       </c>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" spans="1:6">
+    <row r="482" spans="1:6" ht="15.6">
       <c r="A482" s="3">
         <v>478</v>
       </c>
@@ -11284,7 +11288,7 @@
         <v>黃國民.jpg</v>
       </c>
     </row>
-    <row r="483" spans="1:6">
+    <row r="483" spans="1:6" ht="15.6">
       <c r="A483" s="3">
         <v>479</v>
       </c>
@@ -11305,7 +11309,7 @@
         <v>歐贊隊.jpg</v>
       </c>
     </row>
-    <row r="484" spans="1:6">
+    <row r="484" spans="1:6" ht="15.6">
       <c r="A484" s="3">
         <v>480</v>
       </c>
@@ -11326,7 +11330,7 @@
         <v>李朝金.jpg</v>
       </c>
     </row>
-    <row r="485" spans="1:6">
+    <row r="485" spans="1:6" ht="15.6">
       <c r="A485" s="3">
         <v>481</v>
       </c>
@@ -11344,7 +11348,7 @@
       </c>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" spans="1:6">
+    <row r="486" spans="1:6" ht="15.6">
       <c r="A486" s="3">
         <v>482</v>
       </c>
@@ -11365,7 +11369,7 @@
         <v>蔡輝進.jpg</v>
       </c>
     </row>
-    <row r="487" spans="1:6">
+    <row r="487" spans="1:6" ht="15.6">
       <c r="A487" s="3">
         <v>483</v>
       </c>
@@ -11386,7 +11390,7 @@
         <v>楊朝基.jpg</v>
       </c>
     </row>
-    <row r="488" spans="1:6">
+    <row r="488" spans="1:6" ht="15.6">
       <c r="A488" s="3">
         <v>484</v>
       </c>
@@ -11404,7 +11408,7 @@
       </c>
       <c r="F488" s="3"/>
     </row>
-    <row r="489" spans="1:6">
+    <row r="489" spans="1:6" ht="15.6">
       <c r="A489" s="3">
         <v>485</v>
       </c>
@@ -11422,7 +11426,7 @@
       </c>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" spans="1:6">
+    <row r="490" spans="1:6" ht="15.6">
       <c r="A490" s="3">
         <v>486</v>
       </c>
@@ -11440,7 +11444,7 @@
       </c>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" spans="1:6">
+    <row r="491" spans="1:6" ht="15.6">
       <c r="A491" s="3">
         <v>487</v>
       </c>
@@ -11458,7 +11462,7 @@
       </c>
       <c r="F491" s="3"/>
     </row>
-    <row r="492" spans="1:6">
+    <row r="492" spans="1:6" ht="15.6">
       <c r="A492" s="3">
         <v>488</v>
       </c>
@@ -11476,7 +11480,7 @@
       </c>
       <c r="F492" s="3"/>
     </row>
-    <row r="493" spans="1:6">
+    <row r="493" spans="1:6" ht="15.6">
       <c r="A493" s="3">
         <v>489</v>
       </c>
@@ -11497,7 +11501,7 @@
         <v>呂玉華.jpg</v>
       </c>
     </row>
-    <row r="494" spans="1:6">
+    <row r="494" spans="1:6" ht="15.6">
       <c r="A494" s="3">
         <v>490</v>
       </c>
@@ -11515,7 +11519,7 @@
       </c>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" spans="1:6">
+    <row r="495" spans="1:6" ht="15.6">
       <c r="A495" s="3">
         <v>491</v>
       </c>
@@ -11533,7 +11537,7 @@
       </c>
       <c r="F495" s="3"/>
     </row>
-    <row r="496" spans="1:6">
+    <row r="496" spans="1:6" ht="15.6">
       <c r="A496" s="3">
         <v>492</v>
       </c>
@@ -11551,7 +11555,7 @@
       </c>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" spans="1:6">
+    <row r="497" spans="1:6" ht="15.6">
       <c r="A497" s="3">
         <v>493</v>
       </c>
@@ -11572,7 +11576,7 @@
         <v>林照人.jpg</v>
       </c>
     </row>
-    <row r="498" spans="1:6">
+    <row r="498" spans="1:6" ht="15.6">
       <c r="A498" s="3">
         <v>494</v>
       </c>
@@ -11593,7 +11597,7 @@
         <v>林開興.jpg</v>
       </c>
     </row>
-    <row r="499" spans="1:6">
+    <row r="499" spans="1:6" ht="15.6">
       <c r="A499" s="3">
         <v>495</v>
       </c>
@@ -11611,7 +11615,7 @@
       </c>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" spans="1:6">
+    <row r="500" spans="1:6" ht="15.6">
       <c r="A500" s="3">
         <v>496</v>
       </c>
@@ -11629,7 +11633,7 @@
       </c>
       <c r="F500" s="3"/>
     </row>
-    <row r="501" spans="1:6">
+    <row r="501" spans="1:6" ht="15.6">
       <c r="A501" s="3">
         <v>497</v>
       </c>
@@ -11645,7 +11649,7 @@
       <c r="E501" s="5"/>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" spans="1:6">
+    <row r="502" spans="1:6" ht="15.6">
       <c r="A502" s="3">
         <v>498</v>
       </c>
@@ -11661,7 +11665,7 @@
       <c r="E502" s="5"/>
       <c r="F502" s="3"/>
     </row>
-    <row r="503" spans="1:6">
+    <row r="503" spans="1:6" ht="15.6">
       <c r="A503" s="3">
         <v>499</v>
       </c>
@@ -11677,7 +11681,7 @@
       <c r="E503" s="5"/>
       <c r="F503" s="3"/>
     </row>
-    <row r="504" spans="1:6">
+    <row r="504" spans="1:6" ht="15.6">
       <c r="A504" s="3">
         <v>500</v>
       </c>
@@ -11693,7 +11697,7 @@
       <c r="E504" s="5"/>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" spans="1:6">
+    <row r="505" spans="1:6" ht="15.6">
       <c r="A505" s="3">
         <v>501</v>
       </c>
@@ -11709,7 +11713,7 @@
       <c r="E505" s="5"/>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" spans="1:6">
+    <row r="506" spans="1:6" ht="15.6">
       <c r="A506" s="3">
         <v>502</v>
       </c>
@@ -11725,7 +11729,7 @@
       <c r="E506" s="5"/>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" spans="1:6">
+    <row r="507" spans="1:6" ht="15.6">
       <c r="A507" s="3">
         <v>503</v>
       </c>
@@ -11741,7 +11745,7 @@
       <c r="E507" s="5"/>
       <c r="F507" s="3"/>
     </row>
-    <row r="508" spans="1:6">
+    <row r="508" spans="1:6" ht="15.6">
       <c r="A508" s="3">
         <v>504</v>
       </c>
@@ -11757,7 +11761,7 @@
       <c r="E508" s="5"/>
       <c r="F508" s="3"/>
     </row>
-    <row r="509" spans="1:6">
+    <row r="509" spans="1:6" ht="15.6">
       <c r="A509" s="3">
         <v>505</v>
       </c>
@@ -11773,7 +11777,7 @@
       <c r="E509" s="5"/>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" spans="1:6">
+    <row r="510" spans="1:6" ht="15.6">
       <c r="A510" s="3">
         <v>506</v>
       </c>
@@ -11789,7 +11793,7 @@
       <c r="E510" s="5"/>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" spans="1:6">
+    <row r="511" spans="1:6" ht="15.6">
       <c r="A511" s="3">
         <v>507</v>
       </c>
@@ -11805,7 +11809,7 @@
       <c r="E511" s="5"/>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" spans="1:6">
+    <row r="512" spans="1:6" ht="15.6">
       <c r="A512" s="3">
         <v>508</v>
       </c>
@@ -11821,7 +11825,7 @@
       <c r="E512" s="5"/>
       <c r="F512" s="3"/>
     </row>
-    <row r="513" spans="1:6">
+    <row r="513" spans="1:6" ht="15.6">
       <c r="A513" s="3">
         <v>509</v>
       </c>
@@ -11837,7 +11841,7 @@
       <c r="E513" s="5"/>
       <c r="F513" s="3"/>
     </row>
-    <row r="514" spans="1:6">
+    <row r="514" spans="1:6" ht="15.6">
       <c r="A514" s="3">
         <v>510</v>
       </c>
@@ -11853,7 +11857,7 @@
       <c r="E514" s="5"/>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" spans="1:6">
+    <row r="515" spans="1:6" ht="15.6">
       <c r="A515" s="3">
         <v>511</v>
       </c>
@@ -11869,7 +11873,7 @@
       <c r="E515" s="5"/>
       <c r="F515" s="3"/>
     </row>
-    <row r="516" spans="1:6">
+    <row r="516" spans="1:6" ht="15.6">
       <c r="A516" s="3">
         <v>512</v>
       </c>
@@ -11885,7 +11889,7 @@
       <c r="E516" s="5"/>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" spans="1:6">
+    <row r="517" spans="1:6" ht="15.6">
       <c r="A517" s="3">
         <v>513</v>
       </c>
@@ -11901,7 +11905,7 @@
       <c r="E517" s="5"/>
       <c r="F517" s="3"/>
     </row>
-    <row r="518" spans="1:6">
+    <row r="518" spans="1:6" ht="15.6">
       <c r="A518" s="3">
         <v>514</v>
       </c>
@@ -11917,7 +11921,7 @@
       <c r="E518" s="5"/>
       <c r="F518" s="3"/>
     </row>
-    <row r="519" spans="1:6">
+    <row r="519" spans="1:6" ht="15.6">
       <c r="A519" s="3">
         <v>515</v>
       </c>
@@ -11933,7 +11937,7 @@
       <c r="E519" s="5"/>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" spans="1:6">
+    <row r="520" spans="1:6" ht="15.6">
       <c r="A520" s="3">
         <v>516</v>
       </c>
@@ -11949,7 +11953,7 @@
       <c r="E520" s="5"/>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" spans="1:6">
+    <row r="521" spans="1:6" ht="15.6">
       <c r="A521" s="3">
         <v>517</v>
       </c>
@@ -11965,7 +11969,7 @@
       <c r="E521" s="5"/>
       <c r="F521" s="3"/>
     </row>
-    <row r="522" spans="1:6">
+    <row r="522" spans="1:6" ht="15.6">
       <c r="A522" s="3">
         <v>518</v>
       </c>
@@ -11981,7 +11985,7 @@
       <c r="E522" s="5"/>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" spans="1:6">
+    <row r="523" spans="1:6" ht="15.6">
       <c r="A523" s="3">
         <v>519</v>
       </c>
@@ -11997,7 +12001,7 @@
       <c r="E523" s="5"/>
       <c r="F523" s="3"/>
     </row>
-    <row r="524" spans="1:6">
+    <row r="524" spans="1:6" ht="15.6">
       <c r="A524" s="3">
         <v>520</v>
       </c>
@@ -12013,7 +12017,7 @@
       <c r="E524" s="5"/>
       <c r="F524" s="3"/>
     </row>
-    <row r="525" spans="1:6">
+    <row r="525" spans="1:6" ht="15.6">
       <c r="A525" s="3">
         <v>521</v>
       </c>
@@ -12029,7 +12033,7 @@
       <c r="E525" s="5"/>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" spans="1:6">
+    <row r="526" spans="1:6" ht="15.6">
       <c r="A526" s="3">
         <v>522</v>
       </c>
@@ -12045,7 +12049,7 @@
       <c r="E526" s="5"/>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" spans="1:6">
+    <row r="527" spans="1:6" ht="15.6">
       <c r="A527" s="3">
         <v>523</v>
       </c>
@@ -12061,7 +12065,7 @@
       <c r="E527" s="5"/>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" spans="1:6">
+    <row r="528" spans="1:6" ht="15.6">
       <c r="A528" s="3">
         <v>524</v>
       </c>
@@ -12077,7 +12081,7 @@
       <c r="E528" s="5"/>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" spans="1:6">
+    <row r="529" spans="1:6" ht="15.6">
       <c r="A529" s="3">
         <v>525</v>
       </c>
@@ -12093,7 +12097,7 @@
       <c r="E529" s="5"/>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" spans="1:6">
+    <row r="530" spans="1:6" ht="15.6">
       <c r="A530" s="3">
         <v>526</v>
       </c>
@@ -12109,7 +12113,7 @@
       <c r="E530" s="5"/>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" spans="1:6">
+    <row r="531" spans="1:6" ht="15.6">
       <c r="A531" s="3">
         <v>527</v>
       </c>
@@ -12125,7 +12129,7 @@
       <c r="E531" s="5"/>
       <c r="F531" s="3"/>
     </row>
-    <row r="532" spans="1:6">
+    <row r="532" spans="1:6" ht="15.6">
       <c r="A532" s="3">
         <v>528</v>
       </c>
@@ -12141,7 +12145,7 @@
       <c r="E532" s="5"/>
       <c r="F532" s="3"/>
     </row>
-    <row r="533" spans="1:6">
+    <row r="533" spans="1:6" ht="15.6">
       <c r="A533" s="3">
         <v>529</v>
       </c>
@@ -12157,7 +12161,7 @@
       <c r="E533" s="5"/>
       <c r="F533" s="3"/>
     </row>
-    <row r="534" spans="1:6">
+    <row r="534" spans="1:6" ht="15.6">
       <c r="A534" s="3">
         <v>530</v>
       </c>
@@ -12173,7 +12177,7 @@
       <c r="E534" s="5"/>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" spans="1:6">
+    <row r="535" spans="1:6" ht="15.6">
       <c r="A535" s="3">
         <v>531</v>
       </c>
@@ -12189,7 +12193,7 @@
       <c r="E535" s="5"/>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" spans="1:6">
+    <row r="536" spans="1:6" ht="15.6">
       <c r="A536" s="3">
         <v>532</v>
       </c>
@@ -12205,7 +12209,7 @@
       <c r="E536" s="5"/>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" spans="1:6">
+    <row r="537" spans="1:6" ht="15.6">
       <c r="A537" s="3">
         <v>533</v>
       </c>
@@ -12221,7 +12225,7 @@
       <c r="E537" s="5"/>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" spans="1:6">
+    <row r="538" spans="1:6" ht="15.6">
       <c r="A538" s="3">
         <v>534</v>
       </c>
@@ -12237,7 +12241,7 @@
       <c r="E538" s="5"/>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" spans="1:6">
+    <row r="539" spans="1:6" ht="15.6">
       <c r="A539" s="3">
         <v>535</v>
       </c>
@@ -12253,7 +12257,7 @@
       <c r="E539" s="5"/>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" spans="1:6">
+    <row r="540" spans="1:6" ht="15.6">
       <c r="A540" s="3">
         <v>536</v>
       </c>
@@ -12274,7 +12278,7 @@
         <v>吳金贊.jpg</v>
       </c>
     </row>
-    <row r="541" spans="1:6">
+    <row r="541" spans="1:6" ht="15.6">
       <c r="A541" s="3">
         <v>537</v>
       </c>
@@ -12290,7 +12294,7 @@
       <c r="E541" s="5"/>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" spans="1:6">
+    <row r="542" spans="1:6" ht="15.6">
       <c r="A542" s="3">
         <v>538</v>
       </c>
@@ -12306,7 +12310,7 @@
       <c r="E542" s="5"/>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" spans="1:6">
+    <row r="543" spans="1:6" ht="15.6">
       <c r="A543" s="3">
         <v>539</v>
       </c>
@@ -12322,7 +12326,7 @@
       <c r="E543" s="5"/>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" spans="1:6">
+    <row r="544" spans="1:6" ht="15.6">
       <c r="A544" s="3">
         <v>540</v>
       </c>
@@ -12338,7 +12342,7 @@
       <c r="E544" s="5"/>
       <c r="F544" s="3"/>
     </row>
-    <row r="545" spans="1:6">
+    <row r="545" spans="1:6" ht="15.6">
       <c r="A545" s="3">
         <v>541</v>
       </c>
@@ -12354,7 +12358,7 @@
       <c r="E545" s="5"/>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" spans="1:6">
+    <row r="546" spans="1:6" ht="15.6">
       <c r="A546" s="3">
         <v>542</v>
       </c>
@@ -12373,7 +12377,7 @@
         <v>吳有祥.jpg</v>
       </c>
     </row>
-    <row r="547" spans="1:6">
+    <row r="547" spans="1:6" ht="15.6">
       <c r="A547" s="3">
         <v>543</v>
       </c>
